--- a/data/a8-import/アフィリエイト案件_フリーランス案件図鑑.xlsx
+++ b/data/a8-import/アフィリエイト案件_フリーランス案件図鑑.xlsx
@@ -1,1170 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10608"/>
-  </bookViews>
   <sheets>
     <sheet name="programs_a26090353299_202609040" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
-  <si>
-    <t>反映</t>
-  </si>
-  <si>
-    <t>広告主名</t>
-  </si>
-  <si>
-    <t>リンク</t>
-  </si>
-  <si>
-    <t>特徴</t>
-  </si>
-  <si>
-    <t>対応エリア</t>
-  </si>
-  <si>
-    <t>対象年代</t>
-  </si>
-  <si>
-    <t>なにに特化しているか</t>
-  </si>
-  <si>
-    <t>ハズム株式会社</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+EGYBVE+4LJQ+614CY" rel="nofollow"&gt;動画編集スクール【クリエイターズジャパン】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www11.a8.net/0.gif?a8mat=4BC3YO+EGYBVE+4LJQ+614CY" alt=""&gt;</t>
-  </si>
-  <si>
-    <t>■セールスポイント■
-現役の動画クリエイターが教える動画編集スクールです！
-（講師は佐原まい（Youtubeチャンネル登録者数6万人以上）を始め、
-「撮影、PR広告、MV撮影等」が行える映像クリエイターチームでコンテンツ制作を行っております）
-▽クリエイターズジャパン
-[https://www.youtube.com/channel/UCMd5Oj_Ek_jN45XKHqO30Hw](https://www.youtube.com/channel/UCMd5Oj_Ek_jN45XKHqO30Hw)
-▽公式ブログ
-[https://creators-jp.com/](https://creators-jp.com/)
-■サービスの強み■
-・圧倒的なコンテンツ量
-・初心者目線で分かりやすく解説
-・Adobeの操作方法を習得可能（プレミアプロ 、アフターエフェクトなど）
-・案件獲得方法のノウハウ
-・サポート体制の充実度（個別LINE@サポート、オンラインサロン ）
-■オンラインサロン（通称：クリエイターズサロン）
-・受講生のみ参加可能
-・月額1,480円（初月1ヶ月間無料）
-・月1回のZOOM講義＋交流会（不定期セミナー）
-・限定メディアの運営（週2本更新！200記事コンテンツ以上）
-・動画編集案件のご紹介
-※オンラインサロンは、1,000名を超える方に参加いただいており、
-　国内最大級のクリエティブサロンになっています。
-■ターゲットユーザー
-・20代〜40代の男女（50代以上の利用者もいらっしゃいます）
-・在宅ワークを始めたい人
-・フリーランスを目指している人
-・個人で稼ぐのスキルを身につけて起業をしたい人
-・スキマ時間を活用し副収入を得たい人
-■広告主からのメッセージ■
-弊社では、現在YouTubeをメインの集客媒体として活用しております。
-今後、ご紹介頂く際にメディア様の売上UPに直結する様な、
-コンテンツ制作やキャンペーンを行います。</t>
-  </si>
-  <si>
-    <t>全国（オンライン完結）</t>
-  </si>
-  <si>
-    <t>20代〜40代（50代以上の利用者も一部あり）</t>
-  </si>
-  <si>
-    <t>動画編集スキル習得＋案件紹介（オンラインスクール・コミュニティ、Adobe操作習得〜案件獲得ノウハウまで）</t>
-  </si>
-  <si>
-    <t>株式会社ＴＷＯＳＴＯＮＥ＆Ｓｏｎｓ</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+EAEK7U+3TVC+BWVTE" rel="nofollow"&gt;フリーランスエンジニアに安心保証と豊富な案件紹介を【midworks】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www16.a8.net/0.gif?a8mat=4BC3YO+EAEK7U+3TVC+BWVTE" alt=""&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">▼サービス概要
-Midworksは、IT系のフリーランスエンジニア、Webデザイナー（個人事業主）専門のエージェントサービスです。
-▼特徴
-Midworksは豊富な案件と「フリーランス」と「正社員」の、
-良いとこ取りをした働き方を実現する手厚い保障が特徴です。
-・給与保障制度（審査あり）
-・手厚い保障内容で正社員並みの安心感
-・還元率60％超え＆単価公開でクリアな契約
-・常時案件数25,000件以上
-　ご本人に合わせた働き方対応可能
-・エンジニア特化キャリアコンサルタントならではの、
-　長期的な人生の充実を見据えた総合的なアドバイス、手厚いフォロー体制。
-▼ターゲットユーザー
-・ITエンジニア　【20代、30代、40代】
-▼こんなユーザーにおすすめ
-・現在正社員でフリーランスになろうか悩んでいる
-・フリーランスとして働いているが、先行きが不安がある
-　（安定的な案件確保や保障など）
-・自分の市場価値を知りたい、見合った案件で参画したい
-・今後のキャリアビジョンを踏まえて案件を選びたい
-▼メディア様へのメッセージ
-案件数やフリーランスの働き方と正社員並みの保障というイイトコどりな点を
-アピールすることができると、登録に繋がりやすいです！
-登録数、承認件数が高いメディア様には報酬単価も検討致します。
-ご掲載をお待ちしております。
--------------------
-Midworksからのお願い
--------------------
-※副業・時短案件に関しまして※
-現在Midworksでは週4〜5の常駐・リモート案件の取り扱いが多いです。
-一方、週1〜3稼働の案件、副業案件、時短案件のご紹介は難しいです。
-ユーザーの皆様に誤った情報のお届けを防ぎたく、
-「副業、時短案件OK」や、「週１〜週3OK」といった表現は控えていただきたく存じます。
-</t>
-  </si>
-  <si>
-    <t>全国（オンライン対応、週4〜5稼働の常駐・リモート案件中心）</t>
-  </si>
-  <si>
-    <t>20代・30代・40代（ITエンジニア中心）</t>
-  </si>
-  <si>
-    <t>ITフリーランスエンジニア・Webデザイナー（個人事業主）向け案件紹介。給与保障制度・還元率60%超えが特徴</t>
-  </si>
-  <si>
-    <t>株式会社アクロビジョン</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+E8M9EI+4LXM+5YJRM" rel="nofollow"&gt;IT求人ナビフリーランス&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www18.a8.net/0.gif?a8mat=4BC3YO+E8M9EI+4LXM+5YJRM" alt=""&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">▼サービス概要
-IT系のフリーランスエンジニアの方向けのエージェントサービスです。
-◆セールスポイント◆
-・AI技術で豊富な案件数から自動マッチング！
-登録者それぞれにパーソナライズされた案件をタイムリーにメール配信します。
-・全国拠点でIT案件登録数は最大級！
-主に関東を中心にサポートしていますが、全国拠点を活かしフルリモート案件のご案内も可能です。
-(ユーザー様のスキルや該当案件受注後の実績などによって判断されるケースが多いです。)
-・フリーランスの支援実績18年で業界歴が長く、安定感のあるサポートが特徴です。
-・高い報酬で社員のような安心感で稼働。
-業界トップクラスの高単価報酬。
-また、案件が途切れないよう最大限のサポートと今後のキャリアビジョンを踏まえて案内します。
-▼ターゲットユーザー
-ITエンジニア【20〜50代後半】（特に基本設計〜1年以上）
-▼こんなユーザーにおすすめ
-・フリーランスとして働いているが、先行きが不安がある（安定的な案件確保や保障など）
-</t>
-  </si>
-  <si>
-    <t>全国（関東中心、フルリモート案件も対応）</t>
-  </si>
-  <si>
-    <t>20代〜50代後半（ITエンジニア、特に基本設計〜1年以上の経験者）</t>
-  </si>
-  <si>
-    <t>ITフリーランスエンジニア向け案件紹介。AIによる自動マッチングが特徴</t>
-  </si>
-  <si>
-    <t>ＮｅｗＭＡ株式会社</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+1PBO36+5YCE+5YJRM" rel="nofollow"&gt;M&amp;A業界の酸いも甘いも知るプロが導く転職支援【NewMA】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC2EM+1PBO36+5YCE+5YJRM" alt=""&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">◆セールスポイント◆
-・代表自身がM&amp;A業界の実務経験者であり、業界の実情を包み隠さず率直にお伝えします。
-・非公開求人を含むM&amp;A仲介・アドバイザリー領域の厳選求人をご紹介します。
-・書類添削・面接対策から入社後フォローまで、専任コンサルタントが一貫してサポートします。
-・ミスマッチ防止を重視した誠実な情報提供で、長期的なキャリア成功を支援します。
-◆ターゲットユーザー◆
-・法人営業・経営企画・コンサルタントとしての実務経験を持ち、M&amp;A業界へのキャリアチェンジを真剣に検討している25〜40代の方。
-・年収2,000万円超の高インセンティブに魅力を感じつつ、業界の実態や自分の適性について正直なアドバイスを求めている方。
-・大手汎用エージェントでは得られないM&amp;A業界特有の深い知識と率直な情報提供を必要としている方。
-◆おススメの提案の仕方◆
-・「M&amp;A転職エージェントおすすめ比較」記事にて、業界経験者による率直な情報提供という独自性を差別化ポイントとして訴求するのが効果的です。
-・「M&amp;A業界に転職したい」「M&amp;A仲介 適性」などのキーワードに連動した悩み解決型コンテンツで、ミスマッチ防止の誠実さをアピールしてください。
-・「年収1,000万円以上を目指す転職エージェント比較」などのハイキャリア向け記事での紹介もおすすめです。
-</t>
-  </si>
-  <si>
-    <t>全国（オンライン対応）</t>
-  </si>
-  <si>
-    <t>25歳〜40代（法人営業・経営企画・コンサル出身者中心）</t>
-  </si>
-  <si>
-    <t>M&amp;A仲介・アドバイザリー業界特化の転職支援（業界経験者コンサルタントによる率直な情報提供が特徴）</t>
-  </si>
-  <si>
-    <t>株式会社スプラッシュエンジニアリング（SAP特化）</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+E7FE6Y+5N98+5YJRM" rel="nofollow"&gt;SAP特化のITフリーランスの案件紹介サービス【SAPフリーランスバンク】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC3YO+E7FE6Y+5N98+5YJRM" alt=""&gt;</t>
-  </si>
-  <si>
-    <t>SAPフリーランスバンクでは、フリーランスのSAPコンサルタント・
-SAPエンジニアにぴったりの案件をご紹介します。
-■SAPフリーランスバンクとは？
-SAPフリーランスバンクは、SAPに特化したフリーランス案件と
-コンサルタント/エンジニアのマッチングサービスです。
-■SAPフリーランスバンクはこのようなお悩みを解決します
-・自分の市場価値がわからない
-・独立する方法がわからない
-・案件が途切れないか不安
-・SAPを一緒に学ぶ仲間がいない
-■SAPフリーランスバンクの3つの特徴
-・最高月収が200万円
-・月額80万円以上の案件が80%以上
-・リモート率が80%以上</t>
-  </si>
-  <si>
-    <t>全国（オンライン対応、リモート案件中心）</t>
-  </si>
-  <si>
-    <t>制限なし（SAPコンサルタント・エンジニア対象）</t>
-  </si>
-  <si>
-    <t>SAP特化のフリーランス案件紹介（コンサルタント・エンジニア向け）</t>
-  </si>
-  <si>
-    <t>株式会社スプラッシュエンジニアリング（セキュリティ特化）</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+E39CYI+5N98+HV7V6" rel="nofollow"&gt;セキュリティ特化のフリーランス案件紹介サービス【セキュリティプロ・フリーランス】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www14.a8.net/0.gif?a8mat=4BC3YO+E39CYI+5N98+HV7V6" alt=""&gt;</t>
-  </si>
-  <si>
-    <t>セキュリティプロ・フリーランスでは、フリーランスのセキュリティエンジニア・セキュリティコンサルタントにぴったりの案件をご紹介します。
-■セキュリティプロ・フリーランスとは？
-セキュリティプロ・フリーランスは、ITインフラセキュリティにしたフリーランス案件とコンサルタント/エンジニアのマッチングサービスです。
-■セキュリティプロ・フリーランスではこのようなお悩みを解決します
-・自分の市場価値がわからない
-・独立する方法がわからない
-・案件が途切れないか不安
-■セキュリティプロ・フリーランスの3つの特徴
-・最高月収が150万円
-・月額80万円以上の案件が80%以上
-・リモート率が80%以上</t>
-  </si>
-  <si>
-    <t>制限なし（セキュリティエンジニア・コンサルタント対象）</t>
-  </si>
-  <si>
-    <t>セキュリティ特化のフリーランス案件紹介（エンジニア・コンサルタント向け）</t>
-  </si>
-  <si>
-    <t>株式会社Ｇｒｏｏｖｅｍｅｎｔ/Strategy Consultant Bank</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+E3USKA+4SXU+639IQ" rel="nofollow"&gt;ハイクラス向けフリーコンサル案件紹介【Strategy Consultant Bank】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www17.a8.net/0.gif?a8mat=4BC3YO+E3USKA+4SXU+639IQ" alt=""&gt;</t>
-  </si>
-  <si>
-    <t>◆ターゲットユーザー◆
-下記の経歴を持つ20〜40歳台の男女が対象です。
-（1）過去に有名コンサルティングファームで勤務していた経験があり、
-現在は独立してフリーランスとして活動中の方
-（2）過去に有名コンサルティングファームで勤務していた経験があり、
-現在は独立して起業準備中の方
-（3）有名コンサルティングファームでの勤務経験はないが、過去に
-コンサルティングファームのアンダーとして稼働実績のあるフリーランスの方
-◆おススメの提案の仕方◆
-特徴１　高単価の戦略・業務案件が中心
-・戦略ファーム出身者が独自ルートで仕入れた柔軟かつ高単価な上流案件を
-中心にご紹介するため、報酬アップを実現できます
-特徴２　高い案件マッチング精度
-・コンサル出身者が案件紹介を担当するため、他社よりも圧倒的に高いマッチング精度を誇ります
-特徴３　交流会での人脈形成
-稼働コンサルタント向けに、定期的に交流会を実施、ゲストに経営者を招くなど
-実利に繋がる人脈を増やすことができます
-◆広告主からのメッセージ◆
-SCBは私自身の前職の戦略コンサルティングファームでの勤務経験や、
-その後独立して実際にフリーランスのコンサルタントとして活躍する中で
-感じていた課題を解決するためにローンチしたサービスです。
-私は年々発展していくコンサルティング業界に高揚感を抱きつつも、
-コンサルティングファームが大企業化してしまい、コンサルタント各々が
-これまでのように自分でキャリアを切り開いていくことが困難な状況に
-なっていることに課題を感じていました。</t>
-  </si>
-  <si>
-    <t>株式会社Ｇｒｏｏｖｅｍｅｎｔ/IT Consultant Bank</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+ECSAMY+4SXU+HV7V6" rel="nofollow"&gt;業界最大級のフリーのIT・SAPコンサル案件紹介【IT Consultant Bank】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www16.a8.net/0.gif?a8mat=4BC3YO+ECSAMY+4SXU+HV7V6" alt=""&gt;</t>
-  </si>
-  <si>
-    <t>◆ターゲットユーザー◆
-下記の経歴を持つ20〜40歳台の男女が対象です。
-（1）過去に有名コンサルティングファームもしくは、Sierで勤務していた経験があり、
-現在は独立してフリーランスとして活動中の方
-（2）過去に有名コンサルティングファームもしくは、Sierで勤務していた経験があり、
-現在は独立して起業準備中の方
-◆おススメの提案の仕方◆
-特徴１　高単価のIT・SAP案件が中心
-・コンサル出身者が独自ルートで仕入れた柔軟かつ高単価な上流案件を
-中心にご紹介するため、報酬アップを実現できます
-特徴２　高い案件マッチング精度
-・コンサル出身者が案件紹介を担当するため、他社よりも圧倒的に高いマッチング精度を誇ります
-特徴３　交流会での人脈形成
-・稼働コンサルタント向けに、定期的に交流会を実施、ゲストに経営者を招くなど実利に繋がる人脈を増やすことができます
-◆広告主からのメッセージ◆
-弊社はこれまで、Strategy Consultant Bank (https://strategyconsultant-bank.com/）を通じて、
-1,000名を超える優秀なフリーのコンサルタントにご登録いただいており、500件を超える案件をご支援させて頂きました。
-その中で、昨今のDX推進によるシステムの再構築と、IT人材の育成・活用が求められるような機会が増え、
-IT知見を持つコンサルタントのニーズが一層強くなったため、
-今回IT Consultant Bank(ICB)をローンチする運びとなりました。</t>
-  </si>
-  <si>
-    <t>株式会社クラウド人材バンク</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.8671.12290&amp;dna=144763" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.8671.12290&amp;dna=144763" rel="nofollow noopener" target="_blank"&gt;【デジタル人材バンク】&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-①フリーランスのハイスキルなデジタル人材と②企業側の案件とをマッチングするプラットフォームにおいて、①を集客します。（②の企業案件の収集は対象外）
-【案件セールスポイント】
-・高単価の実績※紹介案件の月平均単価（報酬）193万円、最高単価350万円
-・紹介するのは直請け案件中心
-・PwC、アクセンチュア、デロイトトーマツ、リクルート、サイバーエージェント出身のメンバーが候補者の経歴や意向を丁寧にヒアリングし最適な案件を紹介
-・サービス開始から約2.5年で登録者2,000人突破
-【想定検索キーワード】
-・フリーコンサル
-・フリーコンサル案件
-・コンサル 案件紹介
-※「フリー」「フリーランス」「コンサル」「案件」「紹介」を含めば基本見込みが高い
-※その他「SAP」「DX」「PM」「PMO」など
-【ターゲット層】
-・コンサルティングファームや大手Sler出身の20代後半～40代男女</t>
-  </si>
-  <si>
-    <t>株式会社BREXA Technology</t>
-  </si>
-  <si>
-    <t>&lt;img src="http://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10199.14564&amp;dna=166769" border="0" height="1" width="1"&gt;&lt;a href="http://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10199.14564&amp;dna=166769" rel="nofollow noopener" target="_blank"&gt;エンベスト&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-「エンベスト」は、ウェブ業界に特化した人材登録プラットフォームです。
-エンジニアやデザイナーを中心とするクリエイティブなプロフェッショナルが、自身のスキルや実績を登録し、企業やプロジェクトからのオファーを受け取ることができるサービスです。
-利用者は、プロフィール作成やポートフォリオの公開、業務実績のアーカイブなどを通じて、自身のキャリアを可視化し、マーケットでの認知度を高めることができます。
-また、企業側は求めるスキルセットや経験に応じた人材を効率的に検索・採用できる仕組みとなっており、マッチング精度の高さと業界特化型のサービスとして支持されています。
-さらに、最新の求人情報や業界動向、キャリアアップに役立つコンテンツも提供しています。
-【案件セールスポイント】
-業界特化型のエージェント：ウェブ業界に絞ることで、専門性の高い求人情報と人材マッチングを実現。
-利用者にとっては、自身のスキルを正当に評価される環境となります。
-豊富な案件情報：フリーランス案件から正社員の求人まで、幅広い働き方に対応した情報が充実しており、自分のキャリアプランに合わせた選択が可能です。
-充実したサポート体制：キャリアアドバイスや最新の業界情報、スキルアップのためのコンテンツ提供など、利用者の成長を後押しする仕組みが整っています。
-信頼性と実績：株式会社BREXA Technology（旧：株式会社アウトソーシングテクノロジー）というエンジニア系の派遣業界で大手企業が運営
-プロモーションレギュレーション: 広告表現の適正化：事実に基づいた正確な情報提供を徹底し、誇大広告や虚偽の表現を禁止します。
-クリエイティブのルール：利用可能な画像、テキスト、ロゴ等の使用にあたっては、提供素材の改変を行わないこと。
-ターゲット設定の明示：主にウェブ業界のエンジニアやデザイナー層に向けたプロモーションである旨を明記し、ターゲット層以外への過度な訴求は控えます。
-リンクの設置方法：登録や詳細情報へのリンクは、公式サイトのURL（https://enbest.jp/）や専用リンクを正確に記載し、リダイレクトやアフィリエイト特有の追跡コードの付加方法についても事前に確認を行うこと。
-禁止事項：不適切なコンテンツ、著作権侵害、誹謗中傷、及び法令に抵触する表現を一切行わない。また、利用規約やプライバシーポリシーに違反する行為も厳禁とします。
-成果報酬の条件：ユーザー登録完了後の有効なアクションをもって成果と認定し、不正な操作や虚偽の申告による報酬請求は一切認めないものとします。
-モニタリングと改善：広告効果を定期的に分析し、問題が認められた場合には速やかに改善措置を講じる義務を負います。
-その他法令遵守：全てのプロモーション活動は、関連する法令、業界規制および当社内部規定に基づいて実施することを必須とします。</t>
-  </si>
-  <si>
-    <t>株式会社DrivenX</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9043.12849&amp;dna=150482" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9043.12849&amp;dna=150482" rel="nofollow noopener" target="_blank"&gt;ITフリーランス向け案件ダイレクトスカウトサイト【xhours】&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-ITフリーランス向け案件ダイレクトスカウトサイト【xhours】申込促進プロモーション
-【案件セールスポイント】
-xhours（エックスアワーズ）は、ITフリーランス向けの案件ダイレクトスカウトサイトです。希望条件を登録すれば、企業の担当者があなたの経歴や希望条件を見て、あなたに興味をもった企業から希望条件にマッチした精度の高い案件のスカウトが届きます。スカウトのみならず、案件の検索・応募も可能です。 運営は、株式会社DrivenX。「全国の案件とITフリーランスを繋ぎ可能性を広げる」をスローガンとしてサービスを提供している企業が運営しているサービスであり、利用企業数は300社突破しました。多くの企業が利用する案件サービスだからこそ、条件に合った仕事を見つけることができます。
-Xhoursの特徴
-1
-業界最大級の案件数
-エンドや受託会社、SES企業など全国300社以上が利用しています。
-2
-稼働中でも 新たなチャンスを探せる
-エンドや開発会社の担当者とのカジュアルな面談を通じて、次の仕事に繋げることができます。
-3
-担当者が直接スカウト！
-企業の担当者があなたの経歴や希望条件を見て、精度の高いスカウトを行います。
-【想定検索キーワード】
-フリーランスエンジニア関連 プログラミング言語
-【ターゲット層】
-・ITフリーランス
-・20～40代
-・週5日稼動
-・実務経験3年以上
-・関東圏（東京、千葉、神奈川、埼玉）
-・関西圏（大阪、京都、兵庫、奈良、滋賀、和歌山、三重）
-・九州圏（福岡）</t>
-  </si>
-  <si>
-    <t>株式会社Senyou</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10790.15410&amp;dna=175315" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10790.15410&amp;dna=175315" rel="nofollow noopener" target="_blank"&gt;Freelance Port（フリーランスポート）&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-ITフリーランス向けに案件紹介をしているエージェントです。
-登録いただいたエンジニアの方に担当がマッチングをします。
-【案件セールスポイント】
-案件力と信頼性
-キャリアを“仕事で磨く”実戦機会
-価値の提供＝収入になる仕組み
-グローバル対応と越境開発
-“戦友”として挑戦できるコミュニティ文化
-【想定検索キーワード】
-フリーランスエンジニア、フリーランスエージェント、フリーランス案件、PHP案件、Java案件
-【ターゲット層】
-・実務経験3年以上
-・20代後半~40代
-・ITエンジニア、UI/UXデザイナー</t>
-  </si>
-  <si>
-    <t>イグニション・ポイントフォース株式会社</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.7594.10767&amp;dna=130868" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.7594.10767&amp;dna=130868" rel="nofollow noopener" target="_blank"&gt;【アビリティクラウド】&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【案件概要】
-アビリティクラウド｜フリーランスのコンサルタント・エンジニアのマッチングサービスの登録
-【案件セールスポイント】
-DXに関するフリーランスのコンサルタント・エンジニアのマッチングサービス。
-大手のエンドクライアントメインの企業様が多く、商流が浅いのが強み。1次受けや直受けの案件が多いです。
-なので、業務内容も規模が大きく待遇も非常に良い。
-【想定検索キーワード】
-フリーランス　コンサルタント
-フリーランス　エンジニア
-DX　案件
-DX　フリーランス
-【ターゲット層】
-ハイスキルのDXコンサルタント・エンジニア
-</t>
-  </si>
-  <si>
-    <t>アクシスコンサルティング株式会社</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.1332.8389&amp;dna=108223" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.1332.8389&amp;dna=108223" rel="nofollow noopener" target="_blank"&gt;【フリーコンサルBiz |】&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-・正社員紹介業xフリーランスのシナジー効果
-アクシスコンサルティングは外資系・IT業界などハイクラスの転職に強いエージェントです。
-特に、2014年〜19年の大手コンサルティングファーム在籍者の転職支援数第1位など、コンサルティングファームへの転職には圧倒的な実績があります。
-上記のような実績の元、2016年からフリーランス向けの案件紹介事業も開始しました。
-正社員紹介業を通じて構築した幅広い企業ネットワークの中から、
-他社エージェントにはないような単価の高い案件や、最先端の案件をご提案可能です。
-・過去に転職支援した人材様からの案件のご紹介
-弊社で転職支援をした方から、転職先の業務支援の依頼を受けることが多くあります。
-そのようなケースでは、弊社以外のエージェントは利用しておらず、
-完全な弊社独占案件となり、好条件かつ、選考通過率が高い案件をご提案可能です。
-【案件セールスポイント】
-コンサルティング業界およびPEなどから受注する
-独占案件の量および質に強みがあります。
-大手のコンサルティング会社の案件をはじめ、
-事業会社の事業企画ポジションや、PEの投資先のバリューアップ案件など、
-幅広い案件をご提案させて頂きます。
-【ターゲット層】
-20代後半から20代前半のITコンサルタント/戦略コンサルタント
-（BIG４、アクセンチュアなどの総合ファーム、
-もしくは、マッキンゼ―、BCG、ベインなどの戦略ファーム出身者歓迎）</t>
-  </si>
-  <si>
-    <t>株式会社ENZIAN</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9184.13061&amp;dna=152615" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9184.13061&amp;dna=152615" rel="nofollow noopener" target="_blank"&gt;フリーランスエンジニア案件紹介サービス【Lindaws（リンドウズ）】&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-フリーランスとして活躍中、またはこれからフリーランスになろうか検討している
-インフラエンジニアの皆様へ
-インフラ案件のご紹介をさせていただくサービス
-【案件セールスポイント】
-完全インフラ案件に特化
-【想定検索キーワード】
-インフラ、サーバー、クラウド、Windows、Linux、AWS、Azure、GCP
-【ターゲット層】
-フリーランスとして活躍中、またはこれからフリーランスになろうか検討している
-インフラエンジニア
-20～50代の男女
-日本国籍</t>
-  </si>
-  <si>
-    <t>株式会社Wonder Camel</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9354.13289&amp;dna=154959" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9354.13289&amp;dna=154959" rel="nofollow noopener" target="_blank"&gt;quick flow（クイックフロー）&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-SAPフリーランス向け案件マッチングサービス【quick flow（クイックフロー）】面談促進プロモーション
-【案件セールスポイント】
-quickflowは、ERP「SAP」やCRM「Salesforce」を中心としたシステム導入からDX戦略・IT PMOまでDXコンサルが活躍できる案件を豊富に取り扱っている「DXフリーコンサル向け案件マッチングサービス」です。
-◆おススメの提案の仕方◆
-他社サービスとの最大の差別化要素は、「安定したキャッシュフローを実現する報酬の即払い」です。
-従来のマッチングサービスでは、稼働の締め日からフリーコンサルタントが報酬を受け取るまで約45日も掛かってしまいますが、quickflowでは、クライアントからの入金を待たずにフリーコンサルタントの皆さまへ報酬を支払うことで、最短1日での入金を実現しています。
-◆アフィリエイトサイトへのメッセージ◆
-実績を出していただいたアフィリエイトサイト様には特別報酬もご用意しております。ぜひ貴サイトでのご掲載をお願いいたします。
-【想定検索キーワード】
-SAPコンサルタント
-【ターゲット層】
-・これから独立を検討している、独立直後の若手～中堅コンサル
-・SAPやIT PMOなどシステム導入に関する案件をお探しの方</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.5897.8550&amp;dna=109597" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.5897.8550&amp;dna=109597" rel="nofollow noopener" target="_blank"&gt;【IT求人ナビ フリーランス】&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">▼サービス概要
-IT系のフリーランスエンジニアの方向けのエージェントサービスです。
-◆セールスポイント◆
-・AI技術で豊富な案件数から自動マッチング！
-登録者それぞれにパーソナライズされた案件をタイムリーにメール配信します。
-・全国拠点でIT案件登録数は最大級！
-主に関東を中心にサポートしていますが、全国拠点を活かしフルリモート案件のご案内も可能です。
-(ユーザー様のスキルや該当案件受注後の実績などによって判断されるケースが多いです。)
-・フリーランスの支援実績18年で業界歴が長く、安定感のあるサポートが特徴です。
-・高い報酬で社員のような安心感で稼働。
-業界トップクラスの高単価報酬。
-また、案件が途切れないよう最大限のサポートと今後のキャリアビジョンを踏まえて案内します。
-▼ターゲットユーザー
-ITエンジニア【20～50代後半】（特に基本設計〜1年以上）
-▼こんなユーザーにおすすめ
-・フリーランスとして働いているが、先行きが不安がある（安定的な案件確保や保障など）
-</t>
-  </si>
-  <si>
-    <t>株式会社スリーシェイク</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10438.14912&amp;dna=169938" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10438.14912&amp;dna=169938" rel="nofollow noopener" target="_blank"&gt;Relance&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【案件概要】
-Relance（リランス）は、フリーランスのエンジニアに特化した求人・案件紹介サービスです。
-運営会社自体がテックカンパニーの株式会社スリーシェイクであるため、エンジニアの視点に立ったきめ細やかなサポートが特徴です。
-【案件セールスポイント】
-高単価案件が豊富 利用者の平均年収は1,000万円以上。掲載案件の約95%が自社開発やプライム案件なので、不要なマージンが発生せず、スキルが正当に評価された高単価な報酬が期待できます。
-モダンな開発案件が多い スタートアップやベンチャー企業の案件を中心に、GoやTypeScriptといった最新技術を用いるモダンな開発プロジェクトが豊富です。新しい技術に挑戦したいエンジニアにとって魅力的な環境が整っています。
-手厚いキャリアサポート 単に案件を紹介するだけでなく、長期的なキャリア形成をサポートします。フリーランスから正社員への転換支援や、参画企業からのフィードバックを基にしたキャリア相談など、エンジニア一人ひとりの理想のキャリア実現を支援します。
-また、掲載案件の70%以上がフルリモート案件と、柔軟な働き方を希望するエンジニアのニーズにも応えています。
-サービスの利用は、無料の会員登録から始まり、エージェントとの面談、案件紹介、企業との面談、契約、稼働開始という流れで進みます。エンジニアの可能性を広げ、市場価値の高い人材になるためのサポートを提供しています。
-【想定検索キーワード】
-フリーランスエンジニア案件 itフリーランス
-【ターゲット層】
-20代～50代　男性　フリーランスエンジニア
-</t>
-  </si>
-  <si>
-    <t>株式会社Regrit Partners</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.6983.9950&amp;dna=122666" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.6983.9950&amp;dna=122666" rel="nofollow noopener" target="_blank"&gt;foRPro(フォープロ)&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-foRProはコンサルタント経験のあるプロのフリーランスをメイン対象とした、
-独自保有案件・高単価案件をご紹介するプロジェクトマッチングサービスです。
-【案件セールスポイント】
-foRProにご登録いただいているプロフェッショナルは多岐に渡ります。
-コンサルタントご経験者（戦略・業務/オペレーション・IT/テクノロジー）
-その他、新規事業/事業開発・Webマーケティングご経験者など
-（1）DX関連プロジェクト特化型
-昨今取り組みが加速しているDX関連のプロジェクトを中心とした案件を多数保有しております。
-DX構想策定のような戦略案件からオペレーション・業務改革・デジタルツール導入・システム刷新の案件など多岐に渡ります。
-（2）プライム案件&amp;非公開案件多数
-コンサルティングファームや事業会社などの大手・優良企業を中心とした案件を取り扱っています。
-案件の多くがプライム案件となっているため、高単価かつプロの皆様への還元率が高くなっています。
-（3）案件平均単価 150~200万円
-プライム案件を多く抱えていることから余分な手数料が発生せず、案件平均単価150～200万円を実現。
-※100％稼働時の単価戦略・新規事業案件やPMポジションとしての案件などニーズの高い案件を高単価でご紹介いたします。
-【案件の想定検索キーワード】
-フリーランス、フリーコンサル、コンサル
-【ターゲット層】
-男女比　男8：女2
-大手コンサルティングファーム出身者、関東在住、30代前半～50代前半
-エリア指定あり:1都3県（東京都、神奈川県、千葉県、埼玉県）</t>
-  </si>
-  <si>
-    <t>株式会社スプラッシュエンジニアリング</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9610.13659&amp;dna=158376" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9610.13659&amp;dna=158376" rel="nofollow noopener" target="_blank"&gt;SAPフリーランスバンク&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-SAPフリーランスバンクでは、フリーランスのSAPコンサルタント・
-SAPエンジニアにぴったりの案件をご紹介します。
-■SAPフリーランスバンクとは？
-SAPフリーランスバンクは、SAPに特化したフリーランス案件と
-コンサルタント/エンジニアのマッチングサービスです。
-■SAPフリーランスバンクはこのようなお悩みを解決します
-・自分の市場価値がわからない
-・独立する方法がわからない
-・案件が途切れないか不安
-・SAPを一緒に学ぶ仲間がいない
-※SAPとは？
-業務で使用されるシステム（会計システム・在庫管理システム・購買システム・販売システム・生産システムなど）がマルっと入ったパッケージソフトをERPパッケージと言います。
-SAPはERPパッケージの1つで世界でトップのシェアを誇り、日本でも多くの大手企業が導入しています。
-【案件セールスポイント】
-■SAPフリーランスバンクの3つの特徴
-・最高月収が200万円
-・月額80万円以上の案件が80%以上
-・リモート率が80%以上
-【想定検索キーワード】
-SAP、フリーランス、案件、独立
-【ターゲット層】
-SAPコンサルタント、SAPエンジニアとして活躍しているフリーランスの方。
-上記職種でフリーランスとして独立したい方。</t>
-  </si>
-  <si>
-    <t>EBAテック株式会社</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9959.14208&amp;dna=163501" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9959.14208&amp;dna=163501" rel="nofollow noopener" target="_blank"&gt;EBAフリーランス&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【案件概要】 【クローズドASP限定】ITエンジニア向けマッチングサービス「EBAフリーランス」スタート！　
-高単価ITフリーランス案件多数！
-【案件セールスポイント】
-この度、弊社ではITフリーランスの皆様に向けたマッチングサービスを新たに開始いたしました。つきましては、貴サイトでご紹介いただきたく存じます。
-EBAフリーランスはIT分野で成長を続けてきた当社が持つノウハウを使って、全力でエンジニアの成功、成長をバックアップいたします。
-　【EBAフリーランスの強み】
-　・「年収1000万を目指せる！」
-　・「経験豊富な専任パートナーが徹底フォロー！」
-　・「スキルアップや新たな挑戦を支援！エンジニアの人生をサポートします！」
-【想定検索キーワード】
-フリーランス,フリーランス エンジニア,業務委託,業務委託 エンジニア,高単価,高単価 案件,高単価 求人,報酬アップ,単価アップ,月収アップ,年収アップ,最高単価,報酬 100万,報酬 120万,報酬 200万,単価 100万,単価 120万,単価 200万,
-月収 100万,月収 120万,月収 200万,年収 800万,年収 900万,年収 1000万
-年収 1000万,リモート,リモート 案件,リモート 求人,フルリモート,フルリモート 案件,フルリモート 求人,フルリモ,フルリモ 案件,フルリモ 求人,在宅,在宅 案件,在宅 求人,週3,週4,週3 案件,週4 案件,週3 求人,週4 求人,週3 稼働,
-週4 稼働,完全在宅,完全在宅 案件,完全在宅 求人,直案件,非公開案件,スカウト機能,最短24時間,専属コンサルタント,専属営業,継続率,即日
-,
-【ターゲット層】
-・20～30代のフリーランスエンジニア
-・高単価案件を探しているフリーランスエンジニア
-・関東圏在住のフリーランスエンジニア
-・これからフリーランスになりたいエンジニア
-・スキルアップやキャリアチェンジを目指すエンジニア
-</t>
-  </si>
-  <si>
-    <t>ソリッドシード株式会社</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.4369.6489&amp;dna=88605" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.4369.6489&amp;dna=88605" rel="nofollow noopener" target="_blank"&gt;Engineer-Route&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-「エンジニアルート」は、ITに特化したフリーランスのエンジニア/デザイナー専門の案件紹介サイトです。
-【案件セールスポイント】
-他エージェントとは違い、カウンセラーとユーザー（企業）側の担当を分けず、一気通貫で担当しています。
-弊社代表や役員も率先してお会いしておりますので、フリーランスならではのお悩み相談もお聞きしています。
-●メリット
-・業界12年以上の実績
-・代表、役員含め、営業がカウンセリングから参画後の定期フォローまでトータルでケア
-⇒直接お聞きした希望を元に既存の案件紹介、または新規営業活動をしております。
-　実際の営業担当がお話するので、伝言ゲームにならず生の情報をお届けできます。
-・AI、RPA、IoTなどの最新技術から昔から使われている汎用機(AS/400、COBOL)の案件など幅広く対応
-　⇒業種、業務、開発言語などの幅が広いため、どのような年代にもあった案件をご紹介できます。
-・60％のフリーランスが7ヶ月以上の案件に参画（3年以上参画が13％）
-　⇒短期案件、長期案件・近場などご希望に合わせてお探ししています。
-・直接のユーザーや大手企業も多いため、高単価も可能
-・支払サイトは30日以内
-【想定検索キーワード】
-フリーランス　エンジニア、フリーエンジニア、フリーランス　エージェント、
-フリーランス　IT、フリーランス　仕事、フリーランス　求人
-【ターゲット層】
-20代～40代のITエンジニア経験者</t>
-  </si>
-  <si>
-    <t>ボスアーキテクト株式会社</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.6749.9641&amp;dna=119895" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.6749.9641&amp;dna=119895" rel="nofollow noopener" target="_blank"&gt;エンジニアスタイル&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-自由なITフリーランスの働き方を実現する【エンジニアスタイル】
-エンジニアスタイルは、フリーランスのエンジニア・デザイナー向けの案件応募サイトです。
-＜特徴1&gt;
-10万件を超える国内トップレベルの案件掲載数！
-＜特徴2&gt;
-案件応募は1クリックで可能！
-＜特徴3&gt;
-使いやすいUI・UX！案件探しをスムーズに行うことが可能です！
-＜特徴4&gt;
-案件を豊富なこだわり条件から検索可能！リモートワーク、週２稼働、土日稼働OK、未経験可、副業案件、開発スキル、業界・・・など　ご自身の働き方や趣向に合わせてフリーランスの案件をお探しすることが可能です！
-＜特徴5&gt;
-プログラミング言語、職種、エリア、フレームワークなどの相場情報を公開！ご自身のスキルと報酬相場を比較・検討して案件を探すことができます！
-エンジニアスタイルは、『自由なITフリーランスの働き方を実現する』をコンセプトにフリーランスのエンジニア・デザイナーの案件獲得・営業活動を支援します！
-◆オススメの提案の仕方◆
-豊富な案件数からご自身のスキルや働き方に合った案件を見つけることができます。
-他サイトと比べ、きめ細かい条件から案件を探すことができます！
-【想定検索キーワード】
-フリーランス　案件
-副業　案件
-{プログラミング言語名} 案件
-{エンジニア職種名} 案件
-フリーランス　リモート
-副業　リモート
-フリーランス　週2 案件
-フリーランス 土日　案件
-【ターゲット層】
-・フリーランスの20歳～49歳のITエンジニア、デザイナー
-・これからフリーランスを目指す20歳～49歳のITエンジニア、デザイナー
-・本業の傍ら副業を探す20歳～49歳のITエンジニア、デザイナー</t>
-  </si>
-  <si>
-    <t>株式会社ヘルスベイシス</t>
-  </si>
-  <si>
-    <t>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.6738.9628&amp;dna=119763" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.6738.9628&amp;dna=119763" rel="nofollow noopener" target="_blank"&gt;フリコン&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>【案件概要】
-フリーランスのエンジニアとして普段活動されており、新たな案件探しを行っている方を募集します。
-「フリコン」はフリーランスエンジニア特化型エージェントで、皆様の案件探しをご支援しております。
-【案件セールスポイント】
-・高単価案件が多数
-・最短1日で案件参画が決定
-・マージン率も最低3%なのでエンジニアの皆様への還元を最大化
-・約700社との契約実績があるため、様々なスキルのエンジニアにも対応可能
-・週1日〜週5日案件と、案件の幅も広い
-【想定検索キーワード】
-・フリーランスエージェント
-・フリーランスエンジニア エージェント
-・フリーランス 案件
-・フリーランスエンジニア 案件
-【ターゲット層】
-・年代：
-　・20-50代
-　・コアターゲットは30-40代
-・性別：
-　・男女問わない
-　・男性の方が登録者はやや多い
-・ニーズ：
-　・フリーランスとして活動（しようと）している
-　・フリーランス案件を探している</t>
-  </si>
-  <si>
-    <t>株式会社クラウドワークス</t>
-  </si>
-  <si>
-    <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+EAZZTM+2OM2+ZQ80I" rel="nofollow"&gt;クラウドワークス テック&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www16.a8.net/0.gif?a8mat=4BC3YO+EAZZTM+2OM2+ZQ80I" alt=""&gt;</t>
-  </si>
-  <si>
-    <t>◆ サービス概要◆
-『クラウドワークス テック』は、ITエンジニア・Webデザイナーを中心としたフリーランスエージェント・求人紹介サービスです。
-フリーランス登録数 No.1*！ グループ累計600万人以上が登録するクラウドワークスグループだからこそ実現できる
-「高単価」「柔軟な働き方」「充実の福利厚生」を提供しています。
-フリーランス初心者からベテランまで、キャリアアドバイザーが理想の案件探しを徹底支援します。
-*クラウドソーシングを専門に取り扱っている企業（上場企業）において、
-グループ全体でのフリーランス登録数がNo.1（会社発表IR資料比較）
-◆ クラウドワークス テックの特徴◆
-１．フルリモート案件が90%以上
-２．案件継続率90%以上
-３．報酬単価UPの実績多数（全体では約10%のUP率。20〜30%UPの人も。）
-※過去2年稼働実績ある方が対象
-４．週1日〜の副業案件もあり
-５．IT・ベンチャーから自治体・大手まで多種多様な案件
-６．稼働開始後もフォロー担当による手厚いサポート体制（初めて稼働の人は3ヵ月間フォロー）
-７．初心者からベテランまで、個々に適度に寄り添った支援が好評
-８．翌月15日のスピード支払い
-９．作業報告書はWebで簡単・完結
-◆ターゲットユーザー◆
-年齢： 20代後半〜40代
-職種： ITエンジニア、Webデザイナー
-経験： 実務経験2年以上
-属性： 現役フリーランス、独立検討中の方、副業で収入を増やしたい方</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF707070"/>
-      <name val="Noto Sans JP"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1172,316 +64,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1531,10 +125,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1566,10 +160,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1805,5242 +399,5743 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G984"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="34.8833333333333" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="53.5" customWidth="1"/>
-    <col min="5" max="6" width="24.1333333333333" customWidth="1"/>
-    <col min="7" max="7" width="62.25" customWidth="1"/>
-    <col min="8" max="27" width="10" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="9"/>
+    <col min="2" max="2" customWidth="1" width="34.8833333333333"/>
+    <col min="3" max="3" customWidth="1" width="10"/>
+    <col min="4" max="4" customWidth="1" width="53.5"/>
+    <col min="5" max="5" customWidth="1" width="24.1333333333333"/>
+    <col min="6" max="6" customWidth="1" width="24.1333333333333"/>
+    <col min="7" max="7" customWidth="1" width="62.25"/>
+    <col min="8" max="8" customWidth="1" width="10"/>
+    <col min="9" max="9" customWidth="1" width="10"/>
+    <col min="10" max="10" customWidth="1" width="10"/>
+    <col min="11" max="11" customWidth="1" width="10"/>
+    <col min="12" max="12" customWidth="1" width="10"/>
+    <col min="13" max="13" customWidth="1" width="10"/>
+    <col min="14" max="14" customWidth="1" width="10"/>
+    <col min="15" max="15" customWidth="1" width="10"/>
+    <col min="16" max="16" customWidth="1" width="10"/>
+    <col min="17" max="17" customWidth="1" width="10"/>
+    <col min="18" max="18" customWidth="1" width="10"/>
+    <col min="19" max="19" customWidth="1" width="10"/>
+    <col min="20" max="20" customWidth="1" width="10"/>
+    <col min="21" max="21" customWidth="1" width="10"/>
+    <col min="22" max="22" customWidth="1" width="10"/>
+    <col min="23" max="23" customWidth="1" width="10"/>
+    <col min="24" max="24" customWidth="1" width="10"/>
+    <col min="25" max="25" customWidth="1" width="10"/>
+    <col min="26" max="26" customWidth="1" width="10"/>
+    <col min="27" max="27" customWidth="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>反映</v>
+      </c>
+      <c r="B1" t="str">
+        <v>広告主名</v>
+      </c>
+      <c r="C1" t="str">
+        <v>リンク</v>
+      </c>
+      <c r="D1" t="str">
+        <v>特徴</v>
+      </c>
+      <c r="E1" t="str">
+        <v>対応エリア</v>
+      </c>
+      <c r="F1" t="str">
+        <v>対象年代</v>
+      </c>
+      <c r="G1" t="str">
+        <v>なにに特化しているか</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
       <c r="A2" t="b">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="B2" t="str">
+        <v>ハズム株式会社</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+EGYBVE+4LJQ+614CY" rel="nofollow"&gt;動画編集スクール【クリエイターズジャパン】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www11.a8.net/0.gif?a8mat=4BC3YO+EGYBVE+4LJQ+614CY" alt=""&gt;</v>
+      </c>
+      <c r="D2" t="str" xml:space="preserve">
+        <v xml:space="preserve">■セールスポイント■
+現役の動画クリエイターが教える動画編集スクールです！
+（講師は佐原まい（Youtubeチャンネル登録者数6万人以上）を始め、
+「撮影、PR広告、MV撮影等」が行える映像クリエイターチームでコンテンツ制作を行っております）
+▽クリエイターズジャパン
+[https://www.youtube.com/channel/UCMd5Oj_Ek_jN45XKHqO30Hw](https://www.youtube.com/channel/UCMd5Oj_Ek_jN45XKHqO30Hw)
+▽公式ブログ
+[https://creators-jp.com/](https://creators-jp.com/)
+■サービスの強み■
+・圧倒的なコンテンツ量
+・初心者目線で分かりやすく解説
+・Adobeの操作方法を習得可能（プレミアプロ 、アフターエフェクトなど）
+・案件獲得方法のノウハウ
+・サポート体制の充実度（個別LINE@サポート、オンラインサロン ）
+■オンラインサロン（通称：クリエイターズサロン）
+・受講生のみ参加可能
+・月額1,480円（初月1ヶ月間無料）
+・月1回のZOOM講義＋交流会（不定期セミナー）
+・限定メディアの運営（週2本更新！200記事コンテンツ以上）
+・動画編集案件のご紹介
+※オンラインサロンは、1,000名を超える方に参加いただいており、
+　国内最大級のクリエティブサロンになっています。
+■ターゲットユーザー
+・20代〜40代の男女（50代以上の利用者もいらっしゃいます）
+・在宅ワークを始めたい人
+・フリーランスを目指している人
+・個人で稼ぐのスキルを身につけて起業をしたい人
+・スキマ時間を活用し副収入を得たい人
+■広告主からのメッセージ■
+弊社では、現在YouTubeをメインの集客媒体として活用しております。
+今後、ご紹介頂く際にメディア様の売上UPに直結する様な、
+コンテンツ制作やキャンペーンを行います。</v>
+      </c>
+      <c r="E2" t="str">
+        <v>全国（オンライン完結）</v>
+      </c>
+      <c r="F2" t="str">
+        <v>20代〜40代（50代以上の利用者も一部あり）</v>
+      </c>
+      <c r="G2" t="str">
+        <v>動画編集スキル習得＋案件紹介（オンラインスクール・コミュニティ、Adobe操作習得〜案件獲得ノウハウまで）</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="b">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="B3" t="str">
+        <v>株式会社ＴＷＯＳＴＯＮＥ＆Ｓｏｎｓ</v>
+      </c>
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+EAEK7U+3TVC+BWVTE" rel="nofollow"&gt;フリーランスエンジニアに安心保証と豊富な案件紹介を【midworks】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www16.a8.net/0.gif?a8mat=4BC3YO+EAEK7U+3TVC+BWVTE" alt=""&gt;</v>
+      </c>
+      <c r="D3" t="str" xml:space="preserve">
+        <v xml:space="preserve">▼サービス概要
+Midworksは、IT系のフリーランスエンジニア、Webデザイナー（個人事業主）専門のエージェントサービスです。
+▼特徴
+Midworksは豊富な案件と「フリーランス」と「正社員」の、
+良いとこ取りをした働き方を実現する手厚い保障が特徴です。
+・給与保障制度（審査あり）
+・手厚い保障内容で正社員並みの安心感
+・還元率60％超え＆単価公開でクリアな契約
+・常時案件数25,000件以上
+　ご本人に合わせた働き方対応可能
+・エンジニア特化キャリアコンサルタントならではの、
+　長期的な人生の充実を見据えた総合的なアドバイス、手厚いフォロー体制。
+▼ターゲットユーザー
+・ITエンジニア　【20代、30代、40代】
+▼こんなユーザーにおすすめ
+・現在正社員でフリーランスになろうか悩んでいる
+・フリーランスとして働いているが、先行きが不安がある
+　（安定的な案件確保や保障など）
+・自分の市場価値を知りたい、見合った案件で参画したい
+・今後のキャリアビジョンを踏まえて案件を選びたい
+▼メディア様へのメッセージ
+案件数やフリーランスの働き方と正社員並みの保障というイイトコどりな点を
+アピールすることができると、登録に繋がりやすいです！
+登録数、承認件数が高いメディア様には報酬単価も検討致します。
+ご掲載をお待ちしております。
+-------------------
+Midworksからのお願い
+-------------------
+※副業・時短案件に関しまして※
+現在Midworksでは週4〜5の常駐・リモート案件の取り扱いが多いです。
+一方、週1〜3稼働の案件、副業案件、時短案件のご紹介は難しいです。
+ユーザーの皆様に誤った情報のお届けを防ぎたく、
+「副業、時短案件OK」や、「週１〜週3OK」といった表現は控えていただきたく存じます。
+</v>
+      </c>
+      <c r="E3" t="str">
+        <v>全国（オンライン対応、週4〜5稼働の常駐・リモート案件中心）</v>
+      </c>
+      <c r="F3" t="str">
+        <v>20代・30代・40代（ITエンジニア中心）</v>
+      </c>
+      <c r="G3" t="str">
+        <v>ITフリーランスエンジニア・Webデザイナー（個人事業主）向け案件紹介。給与保障制度・還元率60%超えが特徴</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="b">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="B4" t="str">
+        <v>株式会社アクロビジョン</v>
+      </c>
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+E8M9EI+4LXM+5YJRM" rel="nofollow"&gt;IT求人ナビフリーランス&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www18.a8.net/0.gif?a8mat=4BC3YO+E8M9EI+4LXM+5YJRM" alt=""&gt;</v>
+      </c>
+      <c r="D4" t="str" xml:space="preserve">
+        <v xml:space="preserve">▼サービス概要
+IT系のフリーランスエンジニアの方向けのエージェントサービスです。
+◆セールスポイント◆
+・AI技術で豊富な案件数から自動マッチング！
+登録者それぞれにパーソナライズされた案件をタイムリーにメール配信します。
+・全国拠点でIT案件登録数は最大級！
+主に関東を中心にサポートしていますが、全国拠点を活かしフルリモート案件のご案内も可能です。
+(ユーザー様のスキルや該当案件受注後の実績などによって判断されるケースが多いです。)
+・フリーランスの支援実績18年で業界歴が長く、安定感のあるサポートが特徴です。
+・高い報酬で社員のような安心感で稼働。
+業界トップクラスの高単価報酬。
+また、案件が途切れないよう最大限のサポートと今後のキャリアビジョンを踏まえて案内します。
+▼ターゲットユーザー
+ITエンジニア【20〜50代後半】（特に基本設計〜1年以上）
+▼こんなユーザーにおすすめ
+・フリーランスとして働いているが、先行きが不安がある（安定的な案件確保や保障など）
+</v>
+      </c>
+      <c r="E4" t="str">
+        <v>全国（関東中心、フルリモート案件も対応）</v>
+      </c>
+      <c r="F4" t="str">
+        <v>20代〜50代後半（ITエンジニア、特に基本設計〜1年以上の経験者）</v>
+      </c>
+      <c r="G4" t="str">
+        <v>ITフリーランスエンジニア向け案件紹介。AIによる自動マッチングが特徴</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="b">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="B5" t="str">
+        <v>ＮｅｗＭＡ株式会社</v>
+      </c>
+      <c r="C5" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+1PBO36+5YCE+5YJRM" rel="nofollow"&gt;M&amp;A業界の酸いも甘いも知るプロが導く転職支援【NewMA】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC2EM+1PBO36+5YCE+5YJRM" alt=""&gt;</v>
+      </c>
+      <c r="D5" t="str" xml:space="preserve">
+        <v xml:space="preserve">◆セールスポイント◆
+・代表自身がM&amp;A業界の実務経験者であり、業界の実情を包み隠さず率直にお伝えします。
+・非公開求人を含むM&amp;A仲介・アドバイザリー領域の厳選求人をご紹介します。
+・書類添削・面接対策から入社後フォローまで、専任コンサルタントが一貫してサポートします。
+・ミスマッチ防止を重視した誠実な情報提供で、長期的なキャリア成功を支援します。
+◆ターゲットユーザー◆
+・法人営業・経営企画・コンサルタントとしての実務経験を持ち、M&amp;A業界へのキャリアチェンジを真剣に検討している25〜40代の方。
+・年収2,000万円超の高インセンティブに魅力を感じつつ、業界の実態や自分の適性について正直なアドバイスを求めている方。
+・大手汎用エージェントでは得られないM&amp;A業界特有の深い知識と率直な情報提供を必要としている方。
+◆おススメの提案の仕方◆
+・「M&amp;A転職エージェントおすすめ比較」記事にて、業界経験者による率直な情報提供という独自性を差別化ポイントとして訴求するのが効果的です。
+・「M&amp;A業界に転職したい」「M&amp;A仲介 適性」などのキーワードに連動した悩み解決型コンテンツで、ミスマッチ防止の誠実さをアピールしてください。
+・「年収1,000万円以上を目指す転職エージェント比較」などのハイキャリア向け記事での紹介もおすすめです。
+</v>
+      </c>
+      <c r="E5" t="str">
+        <v>全国（オンライン対応）</v>
+      </c>
+      <c r="F5" t="str">
+        <v>25歳〜40代（法人営業・経営企画・コンサル出身者中心）</v>
+      </c>
+      <c r="G5" t="str">
+        <v>M&amp;A仲介・アドバイザリー業界特化の転職支援（業界経験者コンサルタントによる率直な情報提供が特徴）</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
       <c r="A6" t="b">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="B6" t="str">
+        <v>株式会社スプラッシュエンジニアリング（SAP特化）</v>
+      </c>
+      <c r="C6" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+E7FE6Y+5N98+5YJRM" rel="nofollow"&gt;SAP特化のITフリーランスの案件紹介サービス【SAPフリーランスバンク】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC3YO+E7FE6Y+5N98+5YJRM" alt=""&gt;</v>
+      </c>
+      <c r="D6" t="str" xml:space="preserve">
+        <v xml:space="preserve">SAPフリーランスバンクでは、フリーランスのSAPコンサルタント・
+SAPエンジニアにぴったりの案件をご紹介します。
+■SAPフリーランスバンクとは？
+SAPフリーランスバンクは、SAPに特化したフリーランス案件と
+コンサルタント/エンジニアのマッチングサービスです。
+■SAPフリーランスバンクはこのようなお悩みを解決します
+・自分の市場価値がわからない
+・独立する方法がわからない
+・案件が途切れないか不安
+・SAPを一緒に学ぶ仲間がいない
+■SAPフリーランスバンクの3つの特徴
+・最高月収が200万円
+・月額80万円以上の案件が80%以上
+・リモート率が80%以上</v>
+      </c>
+      <c r="E6" t="str">
+        <v>全国（オンライン対応、リモート案件中心）</v>
+      </c>
+      <c r="F6" t="str">
+        <v>制限なし（SAPコンサルタント・エンジニア対象）</v>
+      </c>
+      <c r="G6" t="str">
+        <v>SAP特化のフリーランス案件紹介（コンサルタント・エンジニア向け）</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7" t="b">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="B7" t="str">
+        <v>株式会社スプラッシュエンジニアリング（セキュリティ特化）</v>
+      </c>
+      <c r="C7" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+E39CYI+5N98+HV7V6" rel="nofollow"&gt;セキュリティ特化のフリーランス案件紹介サービス【セキュリティプロ・フリーランス】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www14.a8.net/0.gif?a8mat=4BC3YO+E39CYI+5N98+HV7V6" alt=""&gt;</v>
+      </c>
+      <c r="D7" t="str" xml:space="preserve">
+        <v xml:space="preserve">セキュリティプロ・フリーランスでは、フリーランスのセキュリティエンジニア・セキュリティコンサルタントにぴったりの案件をご紹介します。
+■セキュリティプロ・フリーランスとは？
+セキュリティプロ・フリーランスは、ITインフラセキュリティにしたフリーランス案件とコンサルタント/エンジニアのマッチングサービスです。
+■セキュリティプロ・フリーランスではこのようなお悩みを解決します
+・自分の市場価値がわからない
+・独立する方法がわからない
+・案件が途切れないか不安
+■セキュリティプロ・フリーランスの3つの特徴
+・最高月収が150万円
+・月額80万円以上の案件が80%以上
+・リモート率が80%以上</v>
+      </c>
+      <c r="E7" t="str">
+        <v>全国（オンライン対応、リモート案件中心）</v>
+      </c>
+      <c r="F7" t="str">
+        <v>制限なし（セキュリティエンジニア・コンサルタント対象）</v>
+      </c>
+      <c r="G7" t="str">
+        <v>セキュリティ特化のフリーランス案件紹介（エンジニア・コンサルタント向け）</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
       <c r="A8" t="b">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="B8" t="str">
+        <v>株式会社Ｇｒｏｏｖｅｍｅｎｔ/Strategy Consultant Bank</v>
+      </c>
+      <c r="C8" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+E3USKA+4SXU+639IQ" rel="nofollow"&gt;ハイクラス向けフリーコンサル案件紹介【Strategy Consultant Bank】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www17.a8.net/0.gif?a8mat=4BC3YO+E3USKA+4SXU+639IQ" alt=""&gt;</v>
+      </c>
+      <c r="D8" t="str" xml:space="preserve">
+        <v xml:space="preserve">◆ターゲットユーザー◆
+下記の経歴を持つ20〜40歳台の男女が対象です。
+（1）過去に有名コンサルティングファームで勤務していた経験があり、
+現在は独立してフリーランスとして活動中の方
+（2）過去に有名コンサルティングファームで勤務していた経験があり、
+現在は独立して起業準備中の方
+（3）有名コンサルティングファームでの勤務経験はないが、過去に
+コンサルティングファームのアンダーとして稼働実績のあるフリーランスの方
+◆おススメの提案の仕方◆
+特徴１　高単価の戦略・業務案件が中心
+・戦略ファーム出身者が独自ルートで仕入れた柔軟かつ高単価な上流案件を
+中心にご紹介するため、報酬アップを実現できます
+特徴２　高い案件マッチング精度
+・コンサル出身者が案件紹介を担当するため、他社よりも圧倒的に高いマッチング精度を誇ります
+特徴３　交流会での人脈形成
+稼働コンサルタント向けに、定期的に交流会を実施、ゲストに経営者を招くなど
+実利に繋がる人脈を増やすことができます
+◆広告主からのメッセージ◆
+SCBは私自身の前職の戦略コンサルティングファームでの勤務経験や、
+その後独立して実際にフリーランスのコンサルタントとして活躍する中で
+感じていた課題を解決するためにローンチしたサービスです。
+私は年々発展していくコンサルティング業界に高揚感を抱きつつも、
+コンサルティングファームが大企業化してしまい、コンサルタント各々が
+これまでのように自分でキャリアを切り開いていくことが困難な状況に
+なっていることに課題を感じていました。</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="b">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:4">
+      <c r="B9" t="str">
+        <v>株式会社Ｇｒｏｏｖｅｍｅｎｔ/IT Consultant Bank</v>
+      </c>
+      <c r="C9" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+ECSAMY+4SXU+HV7V6" rel="nofollow"&gt;業界最大級のフリーのIT・SAPコンサル案件紹介【IT Consultant Bank】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www16.a8.net/0.gif?a8mat=4BC3YO+ECSAMY+4SXU+HV7V6" alt=""&gt;</v>
+      </c>
+      <c r="D9" t="str" xml:space="preserve">
+        <v xml:space="preserve">◆ターゲットユーザー◆
+下記の経歴を持つ20〜40歳台の男女が対象です。
+（1）過去に有名コンサルティングファームもしくは、Sierで勤務していた経験があり、
+現在は独立してフリーランスとして活動中の方
+（2）過去に有名コンサルティングファームもしくは、Sierで勤務していた経験があり、
+現在は独立して起業準備中の方
+◆おススメの提案の仕方◆
+特徴１　高単価のIT・SAP案件が中心
+・コンサル出身者が独自ルートで仕入れた柔軟かつ高単価な上流案件を
+中心にご紹介するため、報酬アップを実現できます
+特徴２　高い案件マッチング精度
+・コンサル出身者が案件紹介を担当するため、他社よりも圧倒的に高いマッチング精度を誇ります
+特徴３　交流会での人脈形成
+・稼働コンサルタント向けに、定期的に交流会を実施、ゲストに経営者を招くなど実利に繋がる人脈を増やすことができます
+◆広告主からのメッセージ◆
+弊社はこれまで、Strategy Consultant Bank (https://strategyconsultant-bank.com/）を通じて、
+1,000名を超える優秀なフリーのコンサルタントにご登録いただいており、500件を超える案件をご支援させて頂きました。
+その中で、昨今のDX推進によるシステムの再構築と、IT人材の育成・活用が求められるような機会が増え、
+IT知見を持つコンサルタントのニーズが一層強くなったため、
+今回IT Consultant Bank(ICB)をローンチする運びとなりました。</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" xml:space="preserve">
       <c r="A10" t="b">
         <v>1</v>
       </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:4">
+      <c r="B10" t="str">
+        <v>株式会社クラウド人材バンク</v>
+      </c>
+      <c r="C10" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.8671.12290&amp;dna=144763" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.8671.12290&amp;dna=144763" rel="nofollow noopener" target="_blank"&gt;【デジタル人材バンク】&lt;/a&gt;</v>
+      </c>
+      <c r="D10" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+①フリーランスのハイスキルなデジタル人材と②企業側の案件とをマッチングするプラットフォームにおいて、①を集客します。（②の企業案件の収集は対象外）
+【案件セールスポイント】
+・高単価の実績※紹介案件の月平均単価（報酬）193万円、最高単価350万円
+・紹介するのは直請け案件中心
+・PwC、アクセンチュア、デロイトトーマツ、リクルート、サイバーエージェント出身のメンバーが候補者の経歴や意向を丁寧にヒアリングし最適な案件を紹介
+・サービス開始から約2.5年で登録者2,000人突破
+【想定検索キーワード】
+・フリーコンサル
+・フリーコンサル案件
+・コンサル 案件紹介
+※「フリー」「フリーランス」「コンサル」「案件」「紹介」を含めば基本見込みが高い
+※その他「SAP」「DX」「PM」「PMO」など
+【ターゲット層】
+・コンサルティングファームや大手Sler出身の20代後半～40代男女</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" xml:space="preserve">
       <c r="A11" t="b">
         <v>1</v>
       </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:4">
+      <c r="B11" t="str">
+        <v>株式会社BREXA Technology</v>
+      </c>
+      <c r="C11" t="str">
+        <v>&lt;img src="http://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10199.14564&amp;dna=166769" border="0" height="1" width="1"&gt;&lt;a href="http://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10199.14564&amp;dna=166769" rel="nofollow noopener" target="_blank"&gt;エンベスト&lt;/a&gt;</v>
+      </c>
+      <c r="D11" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+「エンベスト」は、ウェブ業界に特化した人材登録プラットフォームです。
+エンジニアやデザイナーを中心とするクリエイティブなプロフェッショナルが、自身のスキルや実績を登録し、企業やプロジェクトからのオファーを受け取ることができるサービスです。
+利用者は、プロフィール作成やポートフォリオの公開、業務実績のアーカイブなどを通じて、自身のキャリアを可視化し、マーケットでの認知度を高めることができます。
+また、企業側は求めるスキルセットや経験に応じた人材を効率的に検索・採用できる仕組みとなっており、マッチング精度の高さと業界特化型のサービスとして支持されています。
+さらに、最新の求人情報や業界動向、キャリアアップに役立つコンテンツも提供しています。
+【案件セールスポイント】
+業界特化型のエージェント：ウェブ業界に絞ることで、専門性の高い求人情報と人材マッチングを実現。
+利用者にとっては、自身のスキルを正当に評価される環境となります。
+豊富な案件情報：フリーランス案件から正社員の求人まで、幅広い働き方に対応した情報が充実しており、自分のキャリアプランに合わせた選択が可能です。
+充実したサポート体制：キャリアアドバイスや最新の業界情報、スキルアップのためのコンテンツ提供など、利用者の成長を後押しする仕組みが整っています。
+信頼性と実績：株式会社BREXA Technology（旧：株式会社アウトソーシングテクノロジー）というエンジニア系の派遣業界で大手企業が運営
+プロモーションレギュレーション: 広告表現の適正化：事実に基づいた正確な情報提供を徹底し、誇大広告や虚偽の表現を禁止します。
+クリエイティブのルール：利用可能な画像、テキスト、ロゴ等の使用にあたっては、提供素材の改変を行わないこと。
+ターゲット設定の明示：主にウェブ業界のエンジニアやデザイナー層に向けたプロモーションである旨を明記し、ターゲット層以外への過度な訴求は控えます。
+リンクの設置方法：登録や詳細情報へのリンクは、公式サイトのURL（https://enbest.jp/）や専用リンクを正確に記載し、リダイレクトやアフィリエイト特有の追跡コードの付加方法についても事前に確認を行うこと。
+禁止事項：不適切なコンテンツ、著作権侵害、誹謗中傷、及び法令に抵触する表現を一切行わない。また、利用規約やプライバシーポリシーに違反する行為も厳禁とします。
+成果報酬の条件：ユーザー登録完了後の有効なアクションをもって成果と認定し、不正な操作や虚偽の申告による報酬請求は一切認めないものとします。
+モニタリングと改善：広告効果を定期的に分析し、問題が認められた場合には速やかに改善措置を講じる義務を負います。
+その他法令遵守：全てのプロモーション活動は、関連する法令、業界規制および当社内部規定に基づいて実施することを必須とします。</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" xml:space="preserve">
       <c r="A12" t="b">
         <v>1</v>
       </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:4">
+      <c r="B12" t="str">
+        <v>株式会社DrivenX</v>
+      </c>
+      <c r="C12" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9043.12849&amp;dna=150482" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9043.12849&amp;dna=150482" rel="nofollow noopener" target="_blank"&gt;ITフリーランス向け案件ダイレクトスカウトサイト【xhours】&lt;/a&gt;</v>
+      </c>
+      <c r="D12" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+ITフリーランス向け案件ダイレクトスカウトサイト【xhours】申込促進プロモーション
+【案件セールスポイント】
+xhours（エックスアワーズ）は、ITフリーランス向けの案件ダイレクトスカウトサイトです。希望条件を登録すれば、企業の担当者があなたの経歴や希望条件を見て、あなたに興味をもった企業から希望条件にマッチした精度の高い案件のスカウトが届きます。スカウトのみならず、案件の検索・応募も可能です。 運営は、株式会社DrivenX。「全国の案件とITフリーランスを繋ぎ可能性を広げる」をスローガンとしてサービスを提供している企業が運営しているサービスであり、利用企業数は300社突破しました。多くの企業が利用する案件サービスだからこそ、条件に合った仕事を見つけることができます。
+Xhoursの特徴
+1
+業界最大級の案件数
+エンドや受託会社、SES企業など全国300社以上が利用しています。
+2
+稼働中でも 新たなチャンスを探せる
+エンドや開発会社の担当者とのカジュアルな面談を通じて、次の仕事に繋げることができます。
+3
+担当者が直接スカウト！
+企業の担当者があなたの経歴や希望条件を見て、精度の高いスカウトを行います。
+【想定検索キーワード】
+フリーランスエンジニア関連 プログラミング言語
+【ターゲット層】
+・ITフリーランス
+・20～40代
+・週5日稼動
+・実務経験3年以上
+・関東圏（東京、千葉、神奈川、埼玉）
+・関西圏（大阪、京都、兵庫、奈良、滋賀、和歌山、三重）
+・九州圏（福岡）</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" xml:space="preserve">
       <c r="A13" t="b">
         <v>1</v>
       </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1" spans="1:4">
+      <c r="B13" t="str">
+        <v>株式会社Senyou</v>
+      </c>
+      <c r="C13" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10790.15410&amp;dna=175315" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10790.15410&amp;dna=175315" rel="nofollow noopener" target="_blank"&gt;Freelance Port（フリーランスポート）&lt;/a&gt;</v>
+      </c>
+      <c r="D13" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+ITフリーランス向けに案件紹介をしているエージェントです。
+登録いただいたエンジニアの方に担当がマッチングをします。
+【案件セールスポイント】
+案件力と信頼性
+キャリアを“仕事で磨く”実戦機会
+価値の提供＝収入になる仕組み
+グローバル対応と越境開発
+“戦友”として挑戦できるコミュニティ文化
+【想定検索キーワード】
+フリーランスエンジニア、フリーランスエージェント、フリーランス案件、PHP案件、Java案件
+【ターゲット層】
+・実務経験3年以上
+・20代後半~40代
+・ITエンジニア、UI/UXデザイナー</v>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1" xml:space="preserve">
       <c r="A14" t="b">
         <v>1</v>
       </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1" spans="1:4">
+      <c r="B14" t="str">
+        <v>イグニション・ポイントフォース株式会社</v>
+      </c>
+      <c r="C14" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.7594.10767&amp;dna=130868" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.7594.10767&amp;dna=130868" rel="nofollow noopener" target="_blank"&gt;【アビリティクラウド】&lt;/a&gt;</v>
+      </c>
+      <c r="D14" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+アビリティクラウド｜フリーランスのコンサルタント・エンジニアのマッチングサービスの登録
+【案件セールスポイント】
+DXに関するフリーランスのコンサルタント・エンジニアのマッチングサービス。
+大手のエンドクライアントメインの企業様が多く、商流が浅いのが強み。1次受けや直受けの案件が多いです。
+なので、業務内容も規模が大きく待遇も非常に良い。
+【想定検索キーワード】
+フリーランス　コンサルタント
+フリーランス　エンジニア
+DX　案件
+DX　フリーランス
+【ターゲット層】
+ハイスキルのDXコンサルタント・エンジニア
+</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" xml:space="preserve">
       <c r="A15" t="b">
         <v>1</v>
       </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:4">
+      <c r="B15" t="str">
+        <v>アクシスコンサルティング株式会社</v>
+      </c>
+      <c r="C15" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.1332.8389&amp;dna=108223" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.1332.8389&amp;dna=108223" rel="nofollow noopener" target="_blank"&gt;【フリーコンサルBiz |】&lt;/a&gt;</v>
+      </c>
+      <c r="D15" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+・正社員紹介業xフリーランスのシナジー効果
+アクシスコンサルティングは外資系・IT業界などハイクラスの転職に強いエージェントです。
+特に、2014年〜19年の大手コンサルティングファーム在籍者の転職支援数第1位など、コンサルティングファームへの転職には圧倒的な実績があります。
+上記のような実績の元、2016年からフリーランス向けの案件紹介事業も開始しました。
+正社員紹介業を通じて構築した幅広い企業ネットワークの中から、
+他社エージェントにはないような単価の高い案件や、最先端の案件をご提案可能です。
+・過去に転職支援した人材様からの案件のご紹介
+弊社で転職支援をした方から、転職先の業務支援の依頼を受けることが多くあります。
+そのようなケースでは、弊社以外のエージェントは利用しておらず、
+完全な弊社独占案件となり、好条件かつ、選考通過率が高い案件をご提案可能です。
+【案件セールスポイント】
+コンサルティング業界およびPEなどから受注する
+独占案件の量および質に強みがあります。
+大手のコンサルティング会社の案件をはじめ、
+事業会社の事業企画ポジションや、PEの投資先のバリューアップ案件など、
+幅広い案件をご提案させて頂きます。
+【ターゲット層】
+20代後半から20代前半のITコンサルタント/戦略コンサルタント
+（BIG４、アクセンチュアなどの総合ファーム、
+もしくは、マッキンゼ―、BCG、ベインなどの戦略ファーム出身者歓迎）</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" xml:space="preserve">
       <c r="A16" t="b">
         <v>1</v>
       </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1" spans="1:4">
+      <c r="B16" t="str">
+        <v>株式会社ENZIAN</v>
+      </c>
+      <c r="C16" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9184.13061&amp;dna=152615" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9184.13061&amp;dna=152615" rel="nofollow noopener" target="_blank"&gt;フリーランスエンジニア案件紹介サービス【Lindaws（リンドウズ）】&lt;/a&gt;</v>
+      </c>
+      <c r="D16" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+フリーランスとして活躍中、またはこれからフリーランスになろうか検討している
+インフラエンジニアの皆様へ
+インフラ案件のご紹介をさせていただくサービス
+【案件セールスポイント】
+完全インフラ案件に特化
+【想定検索キーワード】
+インフラ、サーバー、クラウド、Windows、Linux、AWS、Azure、GCP
+【ターゲット層】
+フリーランスとして活躍中、またはこれからフリーランスになろうか検討している
+インフラエンジニア
+20～50代の男女
+日本国籍</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1" xml:space="preserve">
       <c r="A17" t="b">
         <v>1</v>
       </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1" spans="1:4">
+      <c r="B17" t="str">
+        <v>株式会社Wonder Camel</v>
+      </c>
+      <c r="C17" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9354.13289&amp;dna=154959" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9354.13289&amp;dna=154959" rel="nofollow noopener" target="_blank"&gt;quick flow（クイックフロー）&lt;/a&gt;</v>
+      </c>
+      <c r="D17" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+SAPフリーランス向け案件マッチングサービス【quick flow（クイックフロー）】面談促進プロモーション
+【案件セールスポイント】
+quickflowは、ERP「SAP」やCRM「Salesforce」を中心としたシステム導入からDX戦略・IT PMOまでDXコンサルが活躍できる案件を豊富に取り扱っている「DXフリーコンサル向け案件マッチングサービス」です。
+◆おススメの提案の仕方◆
+他社サービスとの最大の差別化要素は、「安定したキャッシュフローを実現する報酬の即払い」です。
+従来のマッチングサービスでは、稼働の締め日からフリーコンサルタントが報酬を受け取るまで約45日も掛かってしまいますが、quickflowでは、クライアントからの入金を待たずにフリーコンサルタントの皆さまへ報酬を支払うことで、最短1日での入金を実現しています。
+◆アフィリエイトサイトへのメッセージ◆
+実績を出していただいたアフィリエイトサイト様には特別報酬もご用意しております。ぜひ貴サイトでのご掲載をお願いいたします。
+【想定検索キーワード】
+SAPコンサルタント
+【ターゲット層】
+・これから独立を検討している、独立直後の若手～中堅コンサル
+・SAPやIT PMOなどシステム導入に関する案件をお探しの方</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" xml:space="preserve">
       <c r="A18" t="b">
         <v>0</v>
       </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" ht="14" customHeight="1" spans="1:4">
+      <c r="B18" t="str">
+        <v>株式会社アクロビジョン</v>
+      </c>
+      <c r="C18" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.5897.8550&amp;dna=109597" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.5897.8550&amp;dna=109597" rel="nofollow noopener" target="_blank"&gt;【IT求人ナビ フリーランス】&lt;/a&gt;</v>
+      </c>
+      <c r="D18" t="str" xml:space="preserve">
+        <v xml:space="preserve">▼サービス概要
+IT系のフリーランスエンジニアの方向けのエージェントサービスです。
+◆セールスポイント◆
+・AI技術で豊富な案件数から自動マッチング！
+登録者それぞれにパーソナライズされた案件をタイムリーにメール配信します。
+・全国拠点でIT案件登録数は最大級！
+主に関東を中心にサポートしていますが、全国拠点を活かしフルリモート案件のご案内も可能です。
+(ユーザー様のスキルや該当案件受注後の実績などによって判断されるケースが多いです。)
+・フリーランスの支援実績18年で業界歴が長く、安定感のあるサポートが特徴です。
+・高い報酬で社員のような安心感で稼働。
+業界トップクラスの高単価報酬。
+また、案件が途切れないよう最大限のサポートと今後のキャリアビジョンを踏まえて案内します。
+▼ターゲットユーザー
+ITエンジニア【20～50代後半】（特に基本設計〜1年以上）
+▼こんなユーザーにおすすめ
+・フリーランスとして働いているが、先行きが不安がある（安定的な案件確保や保障など）
+</v>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1" xml:space="preserve">
       <c r="A19" t="b">
         <v>1</v>
       </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1" spans="1:4">
+      <c r="B19" t="str">
+        <v>株式会社スリーシェイク</v>
+      </c>
+      <c r="C19" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10438.14912&amp;dna=169938" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10438.14912&amp;dna=169938" rel="nofollow noopener" target="_blank"&gt;Relance&lt;/a&gt;</v>
+      </c>
+      <c r="D19" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+Relance（リランス）は、フリーランスのエンジニアに特化した求人・案件紹介サービスです。
+運営会社自体がテックカンパニーの株式会社スリーシェイクであるため、エンジニアの視点に立ったきめ細やかなサポートが特徴です。
+【案件セールスポイント】
+高単価案件が豊富 利用者の平均年収は1,000万円以上。掲載案件の約95%が自社開発やプライム案件なので、不要なマージンが発生せず、スキルが正当に評価された高単価な報酬が期待できます。
+モダンな開発案件が多い スタートアップやベンチャー企業の案件を中心に、GoやTypeScriptといった最新技術を用いるモダンな開発プロジェクトが豊富です。新しい技術に挑戦したいエンジニアにとって魅力的な環境が整っています。
+手厚いキャリアサポート 単に案件を紹介するだけでなく、長期的なキャリア形成をサポートします。フリーランスから正社員への転換支援や、参画企業からのフィードバックを基にしたキャリア相談など、エンジニア一人ひとりの理想のキャリア実現を支援します。
+また、掲載案件の70%以上がフルリモート案件と、柔軟な働き方を希望するエンジニアのニーズにも応えています。
+サービスの利用は、無料の会員登録から始まり、エージェントとの面談、案件紹介、企業との面談、契約、稼働開始という流れで進みます。エンジニアの可能性を広げ、市場価値の高い人材になるためのサポートを提供しています。
+【想定検索キーワード】
+フリーランスエンジニア案件 itフリーランス
+【ターゲット層】
+20代～50代　男性　フリーランスエンジニア
+</v>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1" xml:space="preserve">
       <c r="A20" t="b">
         <v>1</v>
       </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:4">
+      <c r="B20" t="str">
+        <v>株式会社Regrit Partners</v>
+      </c>
+      <c r="C20" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.6983.9950&amp;dna=122666" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.6983.9950&amp;dna=122666" rel="nofollow noopener" target="_blank"&gt;foRPro(フォープロ)&lt;/a&gt;</v>
+      </c>
+      <c r="D20" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+foRProはコンサルタント経験のあるプロのフリーランスをメイン対象とした、
+独自保有案件・高単価案件をご紹介するプロジェクトマッチングサービスです。
+【案件セールスポイント】
+foRProにご登録いただいているプロフェッショナルは多岐に渡ります。
+コンサルタントご経験者（戦略・業務/オペレーション・IT/テクノロジー）
+その他、新規事業/事業開発・Webマーケティングご経験者など
+（1）DX関連プロジェクト特化型
+昨今取り組みが加速しているDX関連のプロジェクトを中心とした案件を多数保有しております。
+DX構想策定のような戦略案件からオペレーション・業務改革・デジタルツール導入・システム刷新の案件など多岐に渡ります。
+（2）プライム案件&amp;非公開案件多数
+コンサルティングファームや事業会社などの大手・優良企業を中心とした案件を取り扱っています。
+案件の多くがプライム案件となっているため、高単価かつプロの皆様への還元率が高くなっています。
+（3）案件平均単価 150~200万円
+プライム案件を多く抱えていることから余分な手数料が発生せず、案件平均単価150～200万円を実現。
+※100％稼働時の単価戦略・新規事業案件やPMポジションとしての案件などニーズの高い案件を高単価でご紹介いたします。
+【案件の想定検索キーワード】
+フリーランス、フリーコンサル、コンサル
+【ターゲット層】
+男女比　男8：女2
+大手コンサルティングファーム出身者、関東在住、30代前半～50代前半
+エリア指定あり:1都3県（東京都、神奈川県、千葉県、埼玉県）</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" xml:space="preserve">
       <c r="A21" t="b">
         <v>1</v>
       </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:4">
+      <c r="B21" t="str">
+        <v>株式会社スプラッシュエンジニアリング</v>
+      </c>
+      <c r="C21" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9610.13659&amp;dna=158376" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9610.13659&amp;dna=158376" rel="nofollow noopener" target="_blank"&gt;SAPフリーランスバンク&lt;/a&gt;</v>
+      </c>
+      <c r="D21" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+SAPフリーランスバンクでは、フリーランスのSAPコンサルタント・
+SAPエンジニアにぴったりの案件をご紹介します。
+■SAPフリーランスバンクとは？
+SAPフリーランスバンクは、SAPに特化したフリーランス案件と
+コンサルタント/エンジニアのマッチングサービスです。
+■SAPフリーランスバンクはこのようなお悩みを解決します
+・自分の市場価値がわからない
+・独立する方法がわからない
+・案件が途切れないか不安
+・SAPを一緒に学ぶ仲間がいない
+※SAPとは？
+業務で使用されるシステム（会計システム・在庫管理システム・購買システム・販売システム・生産システムなど）がマルっと入ったパッケージソフトをERPパッケージと言います。
+SAPはERPパッケージの1つで世界でトップのシェアを誇り、日本でも多くの大手企業が導入しています。
+【案件セールスポイント】
+■SAPフリーランスバンクの3つの特徴
+・最高月収が200万円
+・月額80万円以上の案件が80%以上
+・リモート率が80%以上
+【想定検索キーワード】
+SAP、フリーランス、案件、独立
+【ターゲット層】
+SAPコンサルタント、SAPエンジニアとして活躍しているフリーランスの方。
+上記職種でフリーランスとして独立したい方。</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" xml:space="preserve">
       <c r="A22" t="b">
         <v>1</v>
       </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" ht="21" customHeight="1" spans="1:4">
+      <c r="B22" t="str">
+        <v>EBAテック株式会社</v>
+      </c>
+      <c r="C22" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.9959.14208&amp;dna=163501" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.9959.14208&amp;dna=163501" rel="nofollow noopener" target="_blank"&gt;EBAフリーランス&lt;/a&gt;</v>
+      </c>
+      <c r="D22" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】 【クローズドASP限定】ITエンジニア向けマッチングサービス「EBAフリーランス」スタート！　
+高単価ITフリーランス案件多数！
+【案件セールスポイント】
+この度、弊社ではITフリーランスの皆様に向けたマッチングサービスを新たに開始いたしました。つきましては、貴サイトでご紹介いただきたく存じます。
+EBAフリーランスはIT分野で成長を続けてきた当社が持つノウハウを使って、全力でエンジニアの成功、成長をバックアップいたします。
+　【EBAフリーランスの強み】
+　・「年収1000万を目指せる！」
+　・「経験豊富な専任パートナーが徹底フォロー！」
+　・「スキルアップや新たな挑戦を支援！エンジニアの人生をサポートします！」
+【想定検索キーワード】
+フリーランス,フリーランス エンジニア,業務委託,業務委託 エンジニア,高単価,高単価 案件,高単価 求人,報酬アップ,単価アップ,月収アップ,年収アップ,最高単価,報酬 100万,報酬 120万,報酬 200万,単価 100万,単価 120万,単価 200万,
+月収 100万,月収 120万,月収 200万,年収 800万,年収 900万,年収 1000万
+年収 1000万,リモート,リモート 案件,リモート 求人,フルリモート,フルリモート 案件,フルリモート 求人,フルリモ,フルリモ 案件,フルリモ 求人,在宅,在宅 案件,在宅 求人,週3,週4,週3 案件,週4 案件,週3 求人,週4 求人,週3 稼働,
+週4 稼働,完全在宅,完全在宅 案件,完全在宅 求人,直案件,非公開案件,スカウト機能,最短24時間,専属コンサルタント,専属営業,継続率,即日
+,
+【ターゲット層】
+・20～30代のフリーランスエンジニア
+・高単価案件を探しているフリーランスエンジニア
+・関東圏在住のフリーランスエンジニア
+・これからフリーランスになりたいエンジニア
+・スキルアップやキャリアチェンジを目指すエンジニア
+</v>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1" xml:space="preserve">
       <c r="A23" t="b">
         <v>1</v>
       </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:4">
+      <c r="B23" t="str">
+        <v>ソリッドシード株式会社</v>
+      </c>
+      <c r="C23" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.4369.6489&amp;dna=88605" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.4369.6489&amp;dna=88605" rel="nofollow noopener" target="_blank"&gt;Engineer-Route&lt;/a&gt;</v>
+      </c>
+      <c r="D23" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+「エンジニアルート」は、ITに特化したフリーランスのエンジニア/デザイナー専門の案件紹介サイトです。
+【案件セールスポイント】
+他エージェントとは違い、カウンセラーとユーザー（企業）側の担当を分けず、一気通貫で担当しています。
+弊社代表や役員も率先してお会いしておりますので、フリーランスならではのお悩み相談もお聞きしています。
+●メリット
+・業界12年以上の実績
+・代表、役員含め、営業がカウンセリングから参画後の定期フォローまでトータルでケア
+⇒直接お聞きした希望を元に既存の案件紹介、または新規営業活動をしております。
+　実際の営業担当がお話するので、伝言ゲームにならず生の情報をお届けできます。
+・AI、RPA、IoTなどの最新技術から昔から使われている汎用機(AS/400、COBOL)の案件など幅広く対応
+　⇒業種、業務、開発言語などの幅が広いため、どのような年代にもあった案件をご紹介できます。
+・60％のフリーランスが7ヶ月以上の案件に参画（3年以上参画が13％）
+　⇒短期案件、長期案件・近場などご希望に合わせてお探ししています。
+・直接のユーザーや大手企業も多いため、高単価も可能
+・支払サイトは30日以内
+【想定検索キーワード】
+フリーランス　エンジニア、フリーエンジニア、フリーランス　エージェント、
+フリーランス　IT、フリーランス　仕事、フリーランス　求人
+【ターゲット層】
+20代～40代のITエンジニア経験者</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" xml:space="preserve">
       <c r="A24" t="b">
         <v>1</v>
       </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1" spans="1:4">
+      <c r="B24" t="str">
+        <v>ボスアーキテクト株式会社</v>
+      </c>
+      <c r="C24" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.6749.9641&amp;dna=119895" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.6749.9641&amp;dna=119895" rel="nofollow noopener" target="_blank"&gt;エンジニアスタイル&lt;/a&gt;</v>
+      </c>
+      <c r="D24" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+自由なITフリーランスの働き方を実現する【エンジニアスタイル】
+エンジニアスタイルは、フリーランスのエンジニア・デザイナー向けの案件応募サイトです。
+＜特徴1&gt;
+10万件を超える国内トップレベルの案件掲載数！
+＜特徴2&gt;
+案件応募は1クリックで可能！
+＜特徴3&gt;
+使いやすいUI・UX！案件探しをスムーズに行うことが可能です！
+＜特徴4&gt;
+案件を豊富なこだわり条件から検索可能！リモートワーク、週２稼働、土日稼働OK、未経験可、副業案件、開発スキル、業界・・・など　ご自身の働き方や趣向に合わせてフリーランスの案件をお探しすることが可能です！
+＜特徴5&gt;
+プログラミング言語、職種、エリア、フレームワークなどの相場情報を公開！ご自身のスキルと報酬相場を比較・検討して案件を探すことができます！
+エンジニアスタイルは、『自由なITフリーランスの働き方を実現する』をコンセプトにフリーランスのエンジニア・デザイナーの案件獲得・営業活動を支援します！
+◆オススメの提案の仕方◆
+豊富な案件数からご自身のスキルや働き方に合った案件を見つけることができます。
+他サイトと比べ、きめ細かい条件から案件を探すことができます！
+【想定検索キーワード】
+フリーランス　案件
+副業　案件
+{プログラミング言語名} 案件
+{エンジニア職種名} 案件
+フリーランス　リモート
+副業　リモート
+フリーランス　週2 案件
+フリーランス 土日　案件
+【ターゲット層】
+・フリーランスの20歳～49歳のITエンジニア、デザイナー
+・これからフリーランスを目指す20歳～49歳のITエンジニア、デザイナー
+・本業の傍ら副業を探す20歳～49歳のITエンジニア、デザイナー</v>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1" xml:space="preserve">
       <c r="A25" t="b">
         <v>1</v>
       </c>
-      <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1" spans="1:4">
+      <c r="B25" t="str">
+        <v>株式会社ヘルスベイシス</v>
+      </c>
+      <c r="C25" t="str">
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.6738.9628&amp;dna=119763" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.6738.9628&amp;dna=119763" rel="nofollow noopener" target="_blank"&gt;フリコン&lt;/a&gt;</v>
+      </c>
+      <c r="D25" t="str" xml:space="preserve">
+        <v xml:space="preserve">【案件概要】
+フリーランスのエンジニアとして普段活動されており、新たな案件探しを行っている方を募集します。
+「フリコン」はフリーランスエンジニア特化型エージェントで、皆様の案件探しをご支援しております。
+【案件セールスポイント】
+・高単価案件が多数
+・最短1日で案件参画が決定
+・マージン率も最低3%なのでエンジニアの皆様への還元を最大化
+・約700社との契約実績があるため、様々なスキルのエンジニアにも対応可能
+・週1日〜週5日案件と、案件の幅も広い
+【想定検索キーワード】
+・フリーランスエージェント
+・フリーランスエンジニア エージェント
+・フリーランス 案件
+・フリーランスエンジニア 案件
+【ターゲット層】
+・年代：
+　・20-50代
+　・コアターゲットは30-40代
+・性別：
+　・男女問わない
+　・男性の方が登録者はやや多い
+・ニーズ：
+　・フリーランスとして活動（しようと）している
+　・フリーランス案件を探している</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1" xml:space="preserve">
       <c r="A26" t="b">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>1</v>
+      </c>
+      <c r="B26" t="str">
+        <v>株式会社クラウドワークス</v>
+      </c>
+      <c r="C26" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+EAZZTM+2OM2+ZQ80I" rel="nofollow"&gt;クラウドワークス テック&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www16.a8.net/0.gif?a8mat=4BC3YO+EAZZTM+2OM2+ZQ80I" alt=""&gt;</v>
+      </c>
+      <c r="D26" t="str" xml:space="preserve">
+        <v xml:space="preserve">◆ サービス概要◆
+『クラウドワークス テック』は、ITエンジニア・Webデザイナーを中心としたフリーランスエージェント・求人紹介サービスです。
+フリーランス登録数 No.1*！ グループ累計600万人以上が登録するクラウドワークスグループだからこそ実現できる
+「高単価」「柔軟な働き方」「充実の福利厚生」を提供しています。
+フリーランス初心者からベテランまで、キャリアアドバイザーが理想の案件探しを徹底支援します。
+*クラウドソーシングを専門に取り扱っている企業（上場企業）において、
+グループ全体でのフリーランス登録数がNo.1（会社発表IR資料比較）
+◆ クラウドワークス テックの特徴◆
+１．フルリモート案件が90%以上
+２．案件継続率90%以上
+３．報酬単価UPの実績多数（全体では約10%のUP率。20〜30%UPの人も。）
+※過去2年稼働実績ある方が対象
+４．週1日〜の副業案件もあり
+５．IT・ベンチャーから自治体・大手まで多種多様な案件
+６．稼働開始後もフォロー担当による手厚いサポート体制（初めて稼働の人は3ヵ月間フォロー）
+７．初心者からベテランまで、個々に適度に寄り添った支援が好評
+８．翌月15日のスピード支払い
+９．作業報告書はWebで簡単・完結
+◆ターゲットユーザー◆
+年齢： 20代後半〜40代
+職種： ITエンジニア、Webデザイナー
+経験： 実務経験2年以上
+属性： 現役フリーランス、独立検討中の方、副業で収入を増やしたい方</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28">
       <c r="A28" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29">
       <c r="A29" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30">
       <c r="A30" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31">
       <c r="A31" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32">
       <c r="A32" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33">
       <c r="A33" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34">
       <c r="A34" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35">
       <c r="A35" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36">
       <c r="A36" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37">
       <c r="A37" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38">
       <c r="A38" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39">
       <c r="A39" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40">
       <c r="A40" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41">
       <c r="A41" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42">
       <c r="A42" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43">
       <c r="A43" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44">
       <c r="A44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45">
       <c r="A45" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46">
       <c r="A46" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47">
       <c r="A47" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48">
       <c r="A48" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49">
       <c r="A49" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50">
       <c r="A50" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51">
       <c r="A51" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52">
       <c r="A52" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53">
       <c r="A53" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54">
       <c r="A54" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55">
       <c r="A55" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56">
       <c r="A56" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57">
       <c r="A57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58">
       <c r="A58" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59">
       <c r="A59" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60">
       <c r="A60" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61">
       <c r="A61" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62">
       <c r="A62" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63">
       <c r="A63" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64">
       <c r="A64" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65">
       <c r="A65" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66">
       <c r="A66" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67">
       <c r="A67" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68">
       <c r="A68" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69">
       <c r="A69" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70">
       <c r="A70" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71">
       <c r="A71" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72">
       <c r="A72" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73">
       <c r="A73" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74">
       <c r="A74" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75">
       <c r="A75" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76">
       <c r="A76" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77">
       <c r="A77" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78">
       <c r="A78" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79">
       <c r="A79" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80">
       <c r="A80" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81">
       <c r="A81" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82">
       <c r="A82" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83">
       <c r="A83" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84">
       <c r="A84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85">
       <c r="A85" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86">
       <c r="A86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87">
       <c r="A87" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88">
       <c r="A88" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89">
       <c r="A89" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90">
       <c r="A90" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91">
       <c r="A91" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92">
       <c r="A92" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93">
       <c r="A93" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94">
       <c r="A94" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95">
       <c r="A95" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96">
       <c r="A96" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97">
       <c r="A97" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98">
       <c r="A98" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99">
       <c r="A99" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100">
       <c r="A100" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101">
       <c r="A101" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102">
       <c r="A102" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103">
       <c r="A103" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104">
       <c r="A104" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105">
       <c r="A105" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106">
       <c r="A106" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107">
       <c r="A107" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108">
       <c r="A108" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109">
       <c r="A109" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110">
       <c r="A110" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111">
       <c r="A111" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112">
       <c r="A112" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113">
       <c r="A113" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114">
       <c r="A114" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115">
       <c r="A115" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116">
       <c r="A116" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117">
       <c r="A117" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118">
       <c r="A118" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119">
       <c r="A119" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120">
       <c r="A120" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121">
       <c r="A121" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122">
       <c r="A122" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123">
       <c r="A123" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124">
       <c r="A124" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125">
       <c r="A125" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126">
       <c r="A126" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127">
       <c r="A127" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128">
       <c r="A128" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129">
       <c r="A129" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130">
       <c r="A130" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131">
       <c r="A131" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132">
       <c r="A132" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133">
       <c r="A133" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134">
       <c r="A134" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135">
       <c r="A135" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136">
       <c r="A136" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137">
       <c r="A137" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138">
       <c r="A138" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139">
       <c r="A139" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140">
       <c r="A140" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141">
       <c r="A141" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142">
       <c r="A142" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
+    <row r="143">
       <c r="A143" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
+    <row r="144">
       <c r="A144" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145">
       <c r="A145" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146">
       <c r="A146" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
+    <row r="147">
       <c r="A147" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
+    <row r="148">
       <c r="A148" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
+    <row r="149">
       <c r="A149" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
+    <row r="150">
       <c r="A150" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
+    <row r="151">
       <c r="A151" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
+    <row r="152">
       <c r="A152" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
+    <row r="153">
       <c r="A153" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
+    <row r="154">
       <c r="A154" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
+    <row r="155">
       <c r="A155" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
+    <row r="156">
       <c r="A156" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
+    <row r="157">
       <c r="A157" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
+    <row r="158">
       <c r="A158" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
+    <row r="159">
       <c r="A159" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160">
       <c r="A160" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161">
       <c r="A161" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
+    <row r="162">
       <c r="A162" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
+    <row r="163">
       <c r="A163" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
+    <row r="164">
       <c r="A164" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
+    <row r="165">
       <c r="A165" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
+    <row r="166">
       <c r="A166" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
+    <row r="167">
       <c r="A167" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
+    <row r="168">
       <c r="A168" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
+    <row r="169">
       <c r="A169" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
+    <row r="170">
       <c r="A170" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
+    <row r="171">
       <c r="A171" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
+    <row r="172">
       <c r="A172" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
+    <row r="173">
       <c r="A173" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174">
       <c r="A174" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
+    <row r="175">
       <c r="A175" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176">
       <c r="A176" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177">
       <c r="A177" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
+    <row r="178">
       <c r="A178" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
+    <row r="179">
       <c r="A179" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
+    <row r="180">
       <c r="A180" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
+    <row r="181">
       <c r="A181" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182">
       <c r="A182" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:1">
+    <row r="183">
       <c r="A183" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:1">
+    <row r="184">
       <c r="A184" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:1">
+    <row r="185">
       <c r="A185" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:1">
+    <row r="186">
       <c r="A186" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:1">
+    <row r="187">
       <c r="A187" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:1">
+    <row r="188">
       <c r="A188" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:1">
+    <row r="189">
       <c r="A189" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:1">
+    <row r="190">
       <c r="A190" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:1">
+    <row r="191">
       <c r="A191" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:1">
+    <row r="192">
       <c r="A192" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:1">
+    <row r="193">
       <c r="A193" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:1">
+    <row r="194">
       <c r="A194" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:1">
+    <row r="195">
       <c r="A195" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:1">
+    <row r="196">
       <c r="A196" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:1">
+    <row r="197">
       <c r="A197" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:1">
+    <row r="198">
       <c r="A198" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:1">
+    <row r="199">
       <c r="A199" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:1">
+    <row r="200">
       <c r="A200" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:1">
+    <row r="201">
       <c r="A201" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:1">
+    <row r="202">
       <c r="A202" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:1">
+    <row r="203">
       <c r="A203" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:1">
+    <row r="204">
       <c r="A204" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:1">
+    <row r="205">
       <c r="A205" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:1">
+    <row r="206">
       <c r="A206" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:1">
+    <row r="207">
       <c r="A207" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:1">
+    <row r="208">
       <c r="A208" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:1">
+    <row r="209">
       <c r="A209" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:1">
+    <row r="210">
       <c r="A210" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:1">
+    <row r="211">
       <c r="A211" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:1">
+    <row r="212">
       <c r="A212" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:1">
+    <row r="213">
       <c r="A213" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:1">
+    <row r="214">
       <c r="A214" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:1">
+    <row r="215">
       <c r="A215" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:1">
+    <row r="216">
       <c r="A216" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:1">
+    <row r="217">
       <c r="A217" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:1">
+    <row r="218">
       <c r="A218" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:1">
+    <row r="219">
       <c r="A219" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:1">
+    <row r="220">
       <c r="A220" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:1">
+    <row r="221">
       <c r="A221" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:1">
+    <row r="222">
       <c r="A222" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:1">
+    <row r="223">
       <c r="A223" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:1">
+    <row r="224">
       <c r="A224" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:1">
+    <row r="225">
       <c r="A225" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:1">
+    <row r="226">
       <c r="A226" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:1">
+    <row r="227">
       <c r="A227" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:1">
+    <row r="228">
       <c r="A228" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:1">
+    <row r="229">
       <c r="A229" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:1">
+    <row r="230">
       <c r="A230" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:1">
+    <row r="231">
       <c r="A231" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:1">
+    <row r="232">
       <c r="A232" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:1">
+    <row r="233">
       <c r="A233" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:1">
+    <row r="234">
       <c r="A234" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:1">
+    <row r="235">
       <c r="A235" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:1">
+    <row r="236">
       <c r="A236" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:1">
+    <row r="237">
       <c r="A237" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:1">
+    <row r="238">
       <c r="A238" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:1">
+    <row r="239">
       <c r="A239" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:1">
+    <row r="240">
       <c r="A240" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:1">
+    <row r="241">
       <c r="A241" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:1">
+    <row r="242">
       <c r="A242" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:1">
+    <row r="243">
       <c r="A243" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:1">
+    <row r="244">
       <c r="A244" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:1">
+    <row r="245">
       <c r="A245" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:1">
+    <row r="246">
       <c r="A246" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:1">
+    <row r="247">
       <c r="A247" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:1">
+    <row r="248">
       <c r="A248" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:1">
+    <row r="249">
       <c r="A249" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:1">
+    <row r="250">
       <c r="A250" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:1">
+    <row r="251">
       <c r="A251" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:1">
+    <row r="252">
       <c r="A252" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:1">
+    <row r="253">
       <c r="A253" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:1">
+    <row r="254">
       <c r="A254" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:1">
+    <row r="255">
       <c r="A255" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:1">
+    <row r="256">
       <c r="A256" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:1">
+    <row r="257">
       <c r="A257" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:1">
+    <row r="258">
       <c r="A258" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:1">
+    <row r="259">
       <c r="A259" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:1">
+    <row r="260">
       <c r="A260" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:1">
+    <row r="261">
       <c r="A261" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:1">
+    <row r="262">
       <c r="A262" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:1">
+    <row r="263">
       <c r="A263" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:1">
+    <row r="264">
       <c r="A264" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:1">
+    <row r="265">
       <c r="A265" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:1">
+    <row r="266">
       <c r="A266" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:1">
+    <row r="267">
       <c r="A267" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:1">
+    <row r="268">
       <c r="A268" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:1">
+    <row r="269">
       <c r="A269" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:1">
+    <row r="270">
       <c r="A270" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:1">
+    <row r="271">
       <c r="A271" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:1">
+    <row r="272">
       <c r="A272" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:1">
+    <row r="273">
       <c r="A273" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:1">
+    <row r="274">
       <c r="A274" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:1">
+    <row r="275">
       <c r="A275" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:1">
+    <row r="276">
       <c r="A276" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:1">
+    <row r="277">
       <c r="A277" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:1">
+    <row r="278">
       <c r="A278" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:1">
+    <row r="279">
       <c r="A279" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:1">
+    <row r="280">
       <c r="A280" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:1">
+    <row r="281">
       <c r="A281" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:1">
+    <row r="282">
       <c r="A282" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:1">
+    <row r="283">
       <c r="A283" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:1">
+    <row r="284">
       <c r="A284" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:1">
+    <row r="285">
       <c r="A285" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:1">
+    <row r="286">
       <c r="A286" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:1">
+    <row r="287">
       <c r="A287" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:1">
+    <row r="288">
       <c r="A288" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:1">
+    <row r="289">
       <c r="A289" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:1">
+    <row r="290">
       <c r="A290" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:1">
+    <row r="291">
       <c r="A291" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:1">
+    <row r="292">
       <c r="A292" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:1">
+    <row r="293">
       <c r="A293" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:1">
+    <row r="294">
       <c r="A294" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:1">
+    <row r="295">
       <c r="A295" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:1">
+    <row r="296">
       <c r="A296" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:1">
+    <row r="297">
       <c r="A297" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:1">
+    <row r="298">
       <c r="A298" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:1">
+    <row r="299">
       <c r="A299" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:1">
+    <row r="300">
       <c r="A300" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:1">
+    <row r="301">
       <c r="A301" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:1">
+    <row r="302">
       <c r="A302" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:1">
+    <row r="303">
       <c r="A303" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:1">
+    <row r="304">
       <c r="A304" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:1">
+    <row r="305">
       <c r="A305" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:1">
+    <row r="306">
       <c r="A306" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:1">
+    <row r="307">
       <c r="A307" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:1">
+    <row r="308">
       <c r="A308" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:1">
+    <row r="309">
       <c r="A309" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:1">
+    <row r="310">
       <c r="A310" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:1">
+    <row r="311">
       <c r="A311" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:1">
+    <row r="312">
       <c r="A312" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:1">
+    <row r="313">
       <c r="A313" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:1">
+    <row r="314">
       <c r="A314" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:1">
+    <row r="315">
       <c r="A315" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:1">
+    <row r="316">
       <c r="A316" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:1">
+    <row r="317">
       <c r="A317" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:1">
+    <row r="318">
       <c r="A318" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:1">
+    <row r="319">
       <c r="A319" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:1">
+    <row r="320">
       <c r="A320" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:1">
+    <row r="321">
       <c r="A321" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:1">
+    <row r="322">
       <c r="A322" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:1">
+    <row r="323">
       <c r="A323" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:1">
+    <row r="324">
       <c r="A324" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:1">
+    <row r="325">
       <c r="A325" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:1">
+    <row r="326">
       <c r="A326" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:1">
+    <row r="327">
       <c r="A327" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:1">
+    <row r="328">
       <c r="A328" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:1">
+    <row r="329">
       <c r="A329" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:1">
+    <row r="330">
       <c r="A330" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:1">
+    <row r="331">
       <c r="A331" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:1">
+    <row r="332">
       <c r="A332" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:1">
+    <row r="333">
       <c r="A333" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:1">
+    <row r="334">
       <c r="A334" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:1">
+    <row r="335">
       <c r="A335" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:1">
+    <row r="336">
       <c r="A336" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:1">
+    <row r="337">
       <c r="A337" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:1">
+    <row r="338">
       <c r="A338" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:1">
+    <row r="339">
       <c r="A339" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:1">
+    <row r="340">
       <c r="A340" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:1">
+    <row r="341">
       <c r="A341" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:1">
+    <row r="342">
       <c r="A342" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:1">
+    <row r="343">
       <c r="A343" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:1">
+    <row r="344">
       <c r="A344" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:1">
+    <row r="345">
       <c r="A345" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:1">
+    <row r="346">
       <c r="A346" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:1">
+    <row r="347">
       <c r="A347" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:1">
+    <row r="348">
       <c r="A348" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:1">
+    <row r="349">
       <c r="A349" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:1">
+    <row r="350">
       <c r="A350" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:1">
+    <row r="351">
       <c r="A351" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:1">
+    <row r="352">
       <c r="A352" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:1">
+    <row r="353">
       <c r="A353" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:1">
+    <row r="354">
       <c r="A354" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:1">
+    <row r="355">
       <c r="A355" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:1">
+    <row r="356">
       <c r="A356" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:1">
+    <row r="357">
       <c r="A357" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:1">
+    <row r="358">
       <c r="A358" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:1">
+    <row r="359">
       <c r="A359" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:1">
+    <row r="360">
       <c r="A360" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:1">
+    <row r="361">
       <c r="A361" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:1">
+    <row r="362">
       <c r="A362" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:1">
+    <row r="363">
       <c r="A363" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:1">
+    <row r="364">
       <c r="A364" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:1">
+    <row r="365">
       <c r="A365" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:1">
+    <row r="366">
       <c r="A366" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:1">
+    <row r="367">
       <c r="A367" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:1">
+    <row r="368">
       <c r="A368" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:1">
+    <row r="369">
       <c r="A369" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:1">
+    <row r="370">
       <c r="A370" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:1">
+    <row r="371">
       <c r="A371" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:1">
+    <row r="372">
       <c r="A372" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:1">
+    <row r="373">
       <c r="A373" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:1">
+    <row r="374">
       <c r="A374" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:1">
+    <row r="375">
       <c r="A375" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:1">
+    <row r="376">
       <c r="A376" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:1">
+    <row r="377">
       <c r="A377" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:1">
+    <row r="378">
       <c r="A378" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:1">
+    <row r="379">
       <c r="A379" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:1">
+    <row r="380">
       <c r="A380" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:1">
+    <row r="381">
       <c r="A381" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:1">
+    <row r="382">
       <c r="A382" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:1">
+    <row r="383">
       <c r="A383" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:1">
+    <row r="384">
       <c r="A384" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:1">
+    <row r="385">
       <c r="A385" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:1">
+    <row r="386">
       <c r="A386" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:1">
+    <row r="387">
       <c r="A387" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:1">
+    <row r="388">
       <c r="A388" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:1">
+    <row r="389">
       <c r="A389" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:1">
+    <row r="390">
       <c r="A390" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:1">
+    <row r="391">
       <c r="A391" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:1">
+    <row r="392">
       <c r="A392" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:1">
+    <row r="393">
       <c r="A393" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:1">
+    <row r="394">
       <c r="A394" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:1">
+    <row r="395">
       <c r="A395" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:1">
+    <row r="396">
       <c r="A396" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:1">
+    <row r="397">
       <c r="A397" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:1">
+    <row r="398">
       <c r="A398" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:1">
+    <row r="399">
       <c r="A399" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:1">
+    <row r="400">
       <c r="A400" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:1">
+    <row r="401">
       <c r="A401" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:1">
+    <row r="402">
       <c r="A402" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:1">
+    <row r="403">
       <c r="A403" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:1">
+    <row r="404">
       <c r="A404" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:1">
+    <row r="405">
       <c r="A405" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:1">
+    <row r="406">
       <c r="A406" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:1">
+    <row r="407">
       <c r="A407" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:1">
+    <row r="408">
       <c r="A408" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:1">
+    <row r="409">
       <c r="A409" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:1">
+    <row r="410">
       <c r="A410" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:1">
+    <row r="411">
       <c r="A411" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:1">
+    <row r="412">
       <c r="A412" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:1">
+    <row r="413">
       <c r="A413" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:1">
+    <row r="414">
       <c r="A414" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:1">
+    <row r="415">
       <c r="A415" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:1">
+    <row r="416">
       <c r="A416" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:1">
+    <row r="417">
       <c r="A417" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:1">
+    <row r="418">
       <c r="A418" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:1">
+    <row r="419">
       <c r="A419" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:1">
+    <row r="420">
       <c r="A420" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:1">
+    <row r="421">
       <c r="A421" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:1">
+    <row r="422">
       <c r="A422" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:1">
+    <row r="423">
       <c r="A423" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:1">
+    <row r="424">
       <c r="A424" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:1">
+    <row r="425">
       <c r="A425" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:1">
+    <row r="426">
       <c r="A426" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:1">
+    <row r="427">
       <c r="A427" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:1">
+    <row r="428">
       <c r="A428" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:1">
+    <row r="429">
       <c r="A429" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:1">
+    <row r="430">
       <c r="A430" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:1">
+    <row r="431">
       <c r="A431" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:1">
+    <row r="432">
       <c r="A432" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:1">
+    <row r="433">
       <c r="A433" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:1">
+    <row r="434">
       <c r="A434" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:1">
+    <row r="435">
       <c r="A435" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:1">
+    <row r="436">
       <c r="A436" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:1">
+    <row r="437">
       <c r="A437" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:1">
+    <row r="438">
       <c r="A438" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:1">
+    <row r="439">
       <c r="A439" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:1">
+    <row r="440">
       <c r="A440" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:1">
+    <row r="441">
       <c r="A441" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:1">
+    <row r="442">
       <c r="A442" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:1">
+    <row r="443">
       <c r="A443" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:1">
+    <row r="444">
       <c r="A444" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:1">
+    <row r="445">
       <c r="A445" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:1">
+    <row r="446">
       <c r="A446" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:1">
+    <row r="447">
       <c r="A447" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:1">
+    <row r="448">
       <c r="A448" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:1">
+    <row r="449">
       <c r="A449" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:1">
+    <row r="450">
       <c r="A450" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:1">
+    <row r="451">
       <c r="A451" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:1">
+    <row r="452">
       <c r="A452" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:1">
+    <row r="453">
       <c r="A453" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:1">
+    <row r="454">
       <c r="A454" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:1">
+    <row r="455">
       <c r="A455" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:1">
+    <row r="456">
       <c r="A456" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:1">
+    <row r="457">
       <c r="A457" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:1">
+    <row r="458">
       <c r="A458" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:1">
+    <row r="459">
       <c r="A459" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:1">
+    <row r="460">
       <c r="A460" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:1">
+    <row r="461">
       <c r="A461" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:1">
+    <row r="462">
       <c r="A462" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:1">
+    <row r="463">
       <c r="A463" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:1">
+    <row r="464">
       <c r="A464" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:1">
+    <row r="465">
       <c r="A465" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:1">
+    <row r="466">
       <c r="A466" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:1">
+    <row r="467">
       <c r="A467" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:1">
+    <row r="468">
       <c r="A468" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:1">
+    <row r="469">
       <c r="A469" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:1">
+    <row r="470">
       <c r="A470" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:1">
+    <row r="471">
       <c r="A471" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:1">
+    <row r="472">
       <c r="A472" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:1">
+    <row r="473">
       <c r="A473" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:1">
+    <row r="474">
       <c r="A474" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:1">
+    <row r="475">
       <c r="A475" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:1">
+    <row r="476">
       <c r="A476" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:1">
+    <row r="477">
       <c r="A477" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:1">
+    <row r="478">
       <c r="A478" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:1">
+    <row r="479">
       <c r="A479" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:1">
+    <row r="480">
       <c r="A480" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:1">
+    <row r="481">
       <c r="A481" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:1">
+    <row r="482">
       <c r="A482" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:1">
+    <row r="483">
       <c r="A483" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:1">
+    <row r="484">
       <c r="A484" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:1">
+    <row r="485">
       <c r="A485" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:1">
+    <row r="486">
       <c r="A486" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:1">
+    <row r="487">
       <c r="A487" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:1">
+    <row r="488">
       <c r="A488" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:1">
+    <row r="489">
       <c r="A489" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:1">
+    <row r="490">
       <c r="A490" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:1">
+    <row r="491">
       <c r="A491" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:1">
+    <row r="492">
       <c r="A492" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:1">
+    <row r="493">
       <c r="A493" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:1">
+    <row r="494">
       <c r="A494" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:1">
+    <row r="495">
       <c r="A495" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:1">
+    <row r="496">
       <c r="A496" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:1">
+    <row r="497">
       <c r="A497" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:1">
+    <row r="498">
       <c r="A498" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:1">
+    <row r="499">
       <c r="A499" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:1">
+    <row r="500">
       <c r="A500" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:1">
+    <row r="501">
       <c r="A501" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:1">
+    <row r="502">
       <c r="A502" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:1">
+    <row r="503">
       <c r="A503" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:1">
+    <row r="504">
       <c r="A504" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:1">
+    <row r="505">
       <c r="A505" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:1">
+    <row r="506">
       <c r="A506" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:1">
+    <row r="507">
       <c r="A507" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:1">
+    <row r="508">
       <c r="A508" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:1">
+    <row r="509">
       <c r="A509" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:1">
+    <row r="510">
       <c r="A510" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:1">
+    <row r="511">
       <c r="A511" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:1">
+    <row r="512">
       <c r="A512" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:1">
+    <row r="513">
       <c r="A513" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:1">
+    <row r="514">
       <c r="A514" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:1">
+    <row r="515">
       <c r="A515" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:1">
+    <row r="516">
       <c r="A516" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:1">
+    <row r="517">
       <c r="A517" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:1">
+    <row r="518">
       <c r="A518" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:1">
+    <row r="519">
       <c r="A519" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:1">
+    <row r="520">
       <c r="A520" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:1">
+    <row r="521">
       <c r="A521" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:1">
+    <row r="522">
       <c r="A522" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:1">
+    <row r="523">
       <c r="A523" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:1">
+    <row r="524">
       <c r="A524" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:1">
+    <row r="525">
       <c r="A525" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:1">
+    <row r="526">
       <c r="A526" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:1">
+    <row r="527">
       <c r="A527" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:1">
+    <row r="528">
       <c r="A528" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:1">
+    <row r="529">
       <c r="A529" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:1">
+    <row r="530">
       <c r="A530" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:1">
+    <row r="531">
       <c r="A531" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:1">
+    <row r="532">
       <c r="A532" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:1">
+    <row r="533">
       <c r="A533" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:1">
+    <row r="534">
       <c r="A534" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:1">
+    <row r="535">
       <c r="A535" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:1">
+    <row r="536">
       <c r="A536" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:1">
+    <row r="537">
       <c r="A537" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:1">
+    <row r="538">
       <c r="A538" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:1">
+    <row r="539">
       <c r="A539" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:1">
+    <row r="540">
       <c r="A540" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:1">
+    <row r="541">
       <c r="A541" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:1">
+    <row r="542">
       <c r="A542" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:1">
+    <row r="543">
       <c r="A543" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:1">
+    <row r="544">
       <c r="A544" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:1">
+    <row r="545">
       <c r="A545" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:1">
+    <row r="546">
       <c r="A546" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:1">
+    <row r="547">
       <c r="A547" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:1">
+    <row r="548">
       <c r="A548" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:1">
+    <row r="549">
       <c r="A549" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:1">
+    <row r="550">
       <c r="A550" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:1">
+    <row r="551">
       <c r="A551" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:1">
+    <row r="552">
       <c r="A552" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:1">
+    <row r="553">
       <c r="A553" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:1">
+    <row r="554">
       <c r="A554" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:1">
+    <row r="555">
       <c r="A555" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:1">
+    <row r="556">
       <c r="A556" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:1">
+    <row r="557">
       <c r="A557" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:1">
+    <row r="558">
       <c r="A558" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:1">
+    <row r="559">
       <c r="A559" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:1">
+    <row r="560">
       <c r="A560" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:1">
+    <row r="561">
       <c r="A561" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:1">
+    <row r="562">
       <c r="A562" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:1">
+    <row r="563">
       <c r="A563" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:1">
+    <row r="564">
       <c r="A564" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:1">
+    <row r="565">
       <c r="A565" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:1">
+    <row r="566">
       <c r="A566" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:1">
+    <row r="567">
       <c r="A567" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:1">
+    <row r="568">
       <c r="A568" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:1">
+    <row r="569">
       <c r="A569" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:1">
+    <row r="570">
       <c r="A570" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:1">
+    <row r="571">
       <c r="A571" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:1">
+    <row r="572">
       <c r="A572" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:1">
+    <row r="573">
       <c r="A573" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:1">
+    <row r="574">
       <c r="A574" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:1">
+    <row r="575">
       <c r="A575" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:1">
+    <row r="576">
       <c r="A576" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:1">
+    <row r="577">
       <c r="A577" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:1">
+    <row r="578">
       <c r="A578" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:1">
+    <row r="579">
       <c r="A579" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:1">
+    <row r="580">
       <c r="A580" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:1">
+    <row r="581">
       <c r="A581" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:1">
+    <row r="582">
       <c r="A582" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:1">
+    <row r="583">
       <c r="A583" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:1">
+    <row r="584">
       <c r="A584" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:1">
+    <row r="585">
       <c r="A585" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:1">
+    <row r="586">
       <c r="A586" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:1">
+    <row r="587">
       <c r="A587" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:1">
+    <row r="588">
       <c r="A588" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:1">
+    <row r="589">
       <c r="A589" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:1">
+    <row r="590">
       <c r="A590" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:1">
+    <row r="591">
       <c r="A591" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:1">
+    <row r="592">
       <c r="A592" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:1">
+    <row r="593">
       <c r="A593" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:1">
+    <row r="594">
       <c r="A594" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:1">
+    <row r="595">
       <c r="A595" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:1">
+    <row r="596">
       <c r="A596" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:1">
+    <row r="597">
       <c r="A597" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:1">
+    <row r="598">
       <c r="A598" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:1">
+    <row r="599">
       <c r="A599" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:1">
+    <row r="600">
       <c r="A600" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:1">
+    <row r="601">
       <c r="A601" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:1">
+    <row r="602">
       <c r="A602" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:1">
+    <row r="603">
       <c r="A603" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:1">
+    <row r="604">
       <c r="A604" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:1">
+    <row r="605">
       <c r="A605" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:1">
+    <row r="606">
       <c r="A606" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:1">
+    <row r="607">
       <c r="A607" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:1">
+    <row r="608">
       <c r="A608" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:1">
+    <row r="609">
       <c r="A609" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:1">
+    <row r="610">
       <c r="A610" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:1">
+    <row r="611">
       <c r="A611" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:1">
+    <row r="612">
       <c r="A612" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:1">
+    <row r="613">
       <c r="A613" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:1">
+    <row r="614">
       <c r="A614" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:1">
+    <row r="615">
       <c r="A615" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:1">
+    <row r="616">
       <c r="A616" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:1">
+    <row r="617">
       <c r="A617" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:1">
+    <row r="618">
       <c r="A618" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:1">
+    <row r="619">
       <c r="A619" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:1">
+    <row r="620">
       <c r="A620" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:1">
+    <row r="621">
       <c r="A621" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:1">
+    <row r="622">
       <c r="A622" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:1">
+    <row r="623">
       <c r="A623" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:1">
+    <row r="624">
       <c r="A624" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:1">
+    <row r="625">
       <c r="A625" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:1">
+    <row r="626">
       <c r="A626" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:1">
+    <row r="627">
       <c r="A627" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:1">
+    <row r="628">
       <c r="A628" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:1">
+    <row r="629">
       <c r="A629" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:1">
+    <row r="630">
       <c r="A630" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:1">
+    <row r="631">
       <c r="A631" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:1">
+    <row r="632">
       <c r="A632" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:1">
+    <row r="633">
       <c r="A633" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:1">
+    <row r="634">
       <c r="A634" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:1">
+    <row r="635">
       <c r="A635" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:1">
+    <row r="636">
       <c r="A636" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:1">
+    <row r="637">
       <c r="A637" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:1">
+    <row r="638">
       <c r="A638" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:1">
+    <row r="639">
       <c r="A639" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:1">
+    <row r="640">
       <c r="A640" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:1">
+    <row r="641">
       <c r="A641" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:1">
+    <row r="642">
       <c r="A642" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:1">
+    <row r="643">
       <c r="A643" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:1">
+    <row r="644">
       <c r="A644" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:1">
+    <row r="645">
       <c r="A645" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:1">
+    <row r="646">
       <c r="A646" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:1">
+    <row r="647">
       <c r="A647" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:1">
+    <row r="648">
       <c r="A648" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:1">
+    <row r="649">
       <c r="A649" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:1">
+    <row r="650">
       <c r="A650" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:1">
+    <row r="651">
       <c r="A651" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:1">
+    <row r="652">
       <c r="A652" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:1">
+    <row r="653">
       <c r="A653" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:1">
+    <row r="654">
       <c r="A654" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:1">
+    <row r="655">
       <c r="A655" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:1">
+    <row r="656">
       <c r="A656" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:1">
+    <row r="657">
       <c r="A657" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:1">
+    <row r="658">
       <c r="A658" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:1">
+    <row r="659">
       <c r="A659" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:1">
+    <row r="660">
       <c r="A660" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:1">
+    <row r="661">
       <c r="A661" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:1">
+    <row r="662">
       <c r="A662" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:1">
+    <row r="663">
       <c r="A663" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:1">
+    <row r="664">
       <c r="A664" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:1">
+    <row r="665">
       <c r="A665" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:1">
+    <row r="666">
       <c r="A666" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:1">
+    <row r="667">
       <c r="A667" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:1">
+    <row r="668">
       <c r="A668" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:1">
+    <row r="669">
       <c r="A669" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:1">
+    <row r="670">
       <c r="A670" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:1">
+    <row r="671">
       <c r="A671" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:1">
+    <row r="672">
       <c r="A672" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:1">
+    <row r="673">
       <c r="A673" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:1">
+    <row r="674">
       <c r="A674" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:1">
+    <row r="675">
       <c r="A675" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:1">
+    <row r="676">
       <c r="A676" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:1">
+    <row r="677">
       <c r="A677" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:1">
+    <row r="678">
       <c r="A678" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:1">
+    <row r="679">
       <c r="A679" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:1">
+    <row r="680">
       <c r="A680" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:1">
+    <row r="681">
       <c r="A681" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:1">
+    <row r="682">
       <c r="A682" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:1">
+    <row r="683">
       <c r="A683" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:1">
+    <row r="684">
       <c r="A684" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:1">
+    <row r="685">
       <c r="A685" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:1">
+    <row r="686">
       <c r="A686" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:1">
+    <row r="687">
       <c r="A687" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:1">
+    <row r="688">
       <c r="A688" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:1">
+    <row r="689">
       <c r="A689" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:1">
+    <row r="690">
       <c r="A690" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:1">
+    <row r="691">
       <c r="A691" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="692" spans="1:1">
+    <row r="692">
       <c r="A692" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:1">
+    <row r="693">
       <c r="A693" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:1">
+    <row r="694">
       <c r="A694" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:1">
+    <row r="695">
       <c r="A695" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:1">
+    <row r="696">
       <c r="A696" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:1">
+    <row r="697">
       <c r="A697" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:1">
+    <row r="698">
       <c r="A698" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="699" spans="1:1">
+    <row r="699">
       <c r="A699" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="700" spans="1:1">
+    <row r="700">
       <c r="A700" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:1">
+    <row r="701">
       <c r="A701" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:1">
+    <row r="702">
       <c r="A702" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:1">
+    <row r="703">
       <c r="A703" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:1">
+    <row r="704">
       <c r="A704" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:1">
+    <row r="705">
       <c r="A705" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:1">
+    <row r="706">
       <c r="A706" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:1">
+    <row r="707">
       <c r="A707" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:1">
+    <row r="708">
       <c r="A708" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:1">
+    <row r="709">
       <c r="A709" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:1">
+    <row r="710">
       <c r="A710" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:1">
+    <row r="711">
       <c r="A711" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:1">
+    <row r="712">
       <c r="A712" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:1">
+    <row r="713">
       <c r="A713" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:1">
+    <row r="714">
       <c r="A714" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:1">
+    <row r="715">
       <c r="A715" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:1">
+    <row r="716">
       <c r="A716" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:1">
+    <row r="717">
       <c r="A717" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:1">
+    <row r="718">
       <c r="A718" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:1">
+    <row r="719">
       <c r="A719" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="720" spans="1:1">
+    <row r="720">
       <c r="A720" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:1">
+    <row r="721">
       <c r="A721" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:1">
+    <row r="722">
       <c r="A722" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:1">
+    <row r="723">
       <c r="A723" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:1">
+    <row r="724">
       <c r="A724" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:1">
+    <row r="725">
       <c r="A725" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:1">
+    <row r="726">
       <c r="A726" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:1">
+    <row r="727">
       <c r="A727" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:1">
+    <row r="728">
       <c r="A728" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:1">
+    <row r="729">
       <c r="A729" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:1">
+    <row r="730">
       <c r="A730" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="731" spans="1:1">
+    <row r="731">
       <c r="A731" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="732" spans="1:1">
+    <row r="732">
       <c r="A732" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:1">
+    <row r="733">
       <c r="A733" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:1">
+    <row r="734">
       <c r="A734" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:1">
+    <row r="735">
       <c r="A735" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:1">
+    <row r="736">
       <c r="A736" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="737" spans="1:1">
+    <row r="737">
       <c r="A737" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="738" spans="1:1">
+    <row r="738">
       <c r="A738" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:1">
+    <row r="739">
       <c r="A739" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:1">
+    <row r="740">
       <c r="A740" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:1">
+    <row r="741">
       <c r="A741" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="742" spans="1:1">
+    <row r="742">
       <c r="A742" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="743" spans="1:1">
+    <row r="743">
       <c r="A743" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:1">
+    <row r="744">
       <c r="A744" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:1">
+    <row r="745">
       <c r="A745" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:1">
+    <row r="746">
       <c r="A746" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:1">
+    <row r="747">
       <c r="A747" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:1">
+    <row r="748">
       <c r="A748" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:1">
+    <row r="749">
       <c r="A749" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:1">
+    <row r="750">
       <c r="A750" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:1">
+    <row r="751">
       <c r="A751" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="752" spans="1:1">
+    <row r="752">
       <c r="A752" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:1">
+    <row r="753">
       <c r="A753" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:1">
+    <row r="754">
       <c r="A754" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:1">
+    <row r="755">
       <c r="A755" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:1">
+    <row r="756">
       <c r="A756" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:1">
+    <row r="757">
       <c r="A757" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:1">
+    <row r="758">
       <c r="A758" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:1">
+    <row r="759">
       <c r="A759" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:1">
+    <row r="760">
       <c r="A760" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:1">
+    <row r="761">
       <c r="A761" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:1">
+    <row r="762">
       <c r="A762" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:1">
+    <row r="763">
       <c r="A763" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="764" spans="1:1">
+    <row r="764">
       <c r="A764" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="765" spans="1:1">
+    <row r="765">
       <c r="A765" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="766" spans="1:1">
+    <row r="766">
       <c r="A766" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:1">
+    <row r="767">
       <c r="A767" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="768" spans="1:1">
+    <row r="768">
       <c r="A768" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:1">
+    <row r="769">
       <c r="A769" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="770" spans="1:1">
+    <row r="770">
       <c r="A770" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="771" spans="1:1">
+    <row r="771">
       <c r="A771" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="772" spans="1:1">
+    <row r="772">
       <c r="A772" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="773" spans="1:1">
+    <row r="773">
       <c r="A773" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="774" spans="1:1">
+    <row r="774">
       <c r="A774" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="775" spans="1:1">
+    <row r="775">
       <c r="A775" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="776" spans="1:1">
+    <row r="776">
       <c r="A776" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="777" spans="1:1">
+    <row r="777">
       <c r="A777" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="778" spans="1:1">
+    <row r="778">
       <c r="A778" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:1">
+    <row r="779">
       <c r="A779" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="780" spans="1:1">
+    <row r="780">
       <c r="A780" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="781" spans="1:1">
+    <row r="781">
       <c r="A781" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="782" spans="1:1">
+    <row r="782">
       <c r="A782" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="783" spans="1:1">
+    <row r="783">
       <c r="A783" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="784" spans="1:1">
+    <row r="784">
       <c r="A784" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:1">
+    <row r="785">
       <c r="A785" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="786" spans="1:1">
+    <row r="786">
       <c r="A786" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="787" spans="1:1">
+    <row r="787">
       <c r="A787" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="788" spans="1:1">
+    <row r="788">
       <c r="A788" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="789" spans="1:1">
+    <row r="789">
       <c r="A789" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="790" spans="1:1">
+    <row r="790">
       <c r="A790" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="791" spans="1:1">
+    <row r="791">
       <c r="A791" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="792" spans="1:1">
+    <row r="792">
       <c r="A792" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="793" spans="1:1">
+    <row r="793">
       <c r="A793" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="794" spans="1:1">
+    <row r="794">
       <c r="A794" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="795" spans="1:1">
+    <row r="795">
       <c r="A795" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="796" spans="1:1">
+    <row r="796">
       <c r="A796" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="797" spans="1:1">
+    <row r="797">
       <c r="A797" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="798" spans="1:1">
+    <row r="798">
       <c r="A798" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="799" spans="1:1">
+    <row r="799">
       <c r="A799" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="800" spans="1:1">
+    <row r="800">
       <c r="A800" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:1">
+    <row r="801">
       <c r="A801" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="802" spans="1:1">
+    <row r="802">
       <c r="A802" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="803" spans="1:1">
+    <row r="803">
       <c r="A803" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="804" spans="1:1">
+    <row r="804">
       <c r="A804" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="805" spans="1:1">
+    <row r="805">
       <c r="A805" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="806" spans="1:1">
+    <row r="806">
       <c r="A806" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="807" spans="1:1">
+    <row r="807">
       <c r="A807" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="808" spans="1:1">
+    <row r="808">
       <c r="A808" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="809" spans="1:1">
+    <row r="809">
       <c r="A809" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="810" spans="1:1">
+    <row r="810">
       <c r="A810" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="811" spans="1:1">
+    <row r="811">
       <c r="A811" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="812" spans="1:1">
+    <row r="812">
       <c r="A812" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:1">
+    <row r="813">
       <c r="A813" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:1">
+    <row r="814">
       <c r="A814" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:1">
+    <row r="815">
       <c r="A815" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="816" spans="1:1">
+    <row r="816">
       <c r="A816" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:1">
+    <row r="817">
       <c r="A817" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="818" spans="1:1">
+    <row r="818">
       <c r="A818" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="819" spans="1:1">
+    <row r="819">
       <c r="A819" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="820" spans="1:1">
+    <row r="820">
       <c r="A820" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="821" spans="1:1">
+    <row r="821">
       <c r="A821" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="822" spans="1:1">
+    <row r="822">
       <c r="A822" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="823" spans="1:1">
+    <row r="823">
       <c r="A823" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="824" spans="1:1">
+    <row r="824">
       <c r="A824" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="825" spans="1:1">
+    <row r="825">
       <c r="A825" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="826" spans="1:1">
+    <row r="826">
       <c r="A826" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="827" spans="1:1">
+    <row r="827">
       <c r="A827" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="828" spans="1:1">
+    <row r="828">
       <c r="A828" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="829" spans="1:1">
+    <row r="829">
       <c r="A829" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="830" spans="1:1">
+    <row r="830">
       <c r="A830" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="831" spans="1:1">
+    <row r="831">
       <c r="A831" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="832" spans="1:1">
+    <row r="832">
       <c r="A832" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="833" spans="1:1">
+    <row r="833">
       <c r="A833" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="834" spans="1:1">
+    <row r="834">
       <c r="A834" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="835" spans="1:1">
+    <row r="835">
       <c r="A835" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="836" spans="1:1">
+    <row r="836">
       <c r="A836" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="837" spans="1:1">
+    <row r="837">
       <c r="A837" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="838" spans="1:1">
+    <row r="838">
       <c r="A838" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="839" spans="1:1">
+    <row r="839">
       <c r="A839" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="840" spans="1:1">
+    <row r="840">
       <c r="A840" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="841" spans="1:1">
+    <row r="841">
       <c r="A841" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="842" spans="1:1">
+    <row r="842">
       <c r="A842" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="843" spans="1:1">
+    <row r="843">
       <c r="A843" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="844" spans="1:1">
+    <row r="844">
       <c r="A844" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="845" spans="1:1">
+    <row r="845">
       <c r="A845" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="846" spans="1:1">
+    <row r="846">
       <c r="A846" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="847" spans="1:1">
+    <row r="847">
       <c r="A847" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="848" spans="1:1">
+    <row r="848">
       <c r="A848" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:1">
+    <row r="849">
       <c r="A849" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="850" spans="1:1">
+    <row r="850">
       <c r="A850" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="851" spans="1:1">
+    <row r="851">
       <c r="A851" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="852" spans="1:1">
+    <row r="852">
       <c r="A852" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="853" spans="1:1">
+    <row r="853">
       <c r="A853" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="854" spans="1:1">
+    <row r="854">
       <c r="A854" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="855" spans="1:1">
+    <row r="855">
       <c r="A855" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="856" spans="1:1">
+    <row r="856">
       <c r="A856" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="857" spans="1:1">
+    <row r="857">
       <c r="A857" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="858" spans="1:1">
+    <row r="858">
       <c r="A858" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="859" spans="1:1">
+    <row r="859">
       <c r="A859" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="860" spans="1:1">
+    <row r="860">
       <c r="A860" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="861" spans="1:1">
+    <row r="861">
       <c r="A861" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="862" spans="1:1">
+    <row r="862">
       <c r="A862" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="863" spans="1:1">
+    <row r="863">
       <c r="A863" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="864" spans="1:1">
+    <row r="864">
       <c r="A864" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="865" spans="1:1">
+    <row r="865">
       <c r="A865" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="866" spans="1:1">
+    <row r="866">
       <c r="A866" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="867" spans="1:1">
+    <row r="867">
       <c r="A867" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="868" spans="1:1">
+    <row r="868">
       <c r="A868" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="869" spans="1:1">
+    <row r="869">
       <c r="A869" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="870" spans="1:1">
+    <row r="870">
       <c r="A870" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="871" spans="1:1">
+    <row r="871">
       <c r="A871" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="872" spans="1:1">
+    <row r="872">
       <c r="A872" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="873" spans="1:1">
+    <row r="873">
       <c r="A873" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="874" spans="1:1">
+    <row r="874">
       <c r="A874" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="875" spans="1:1">
+    <row r="875">
       <c r="A875" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="876" spans="1:1">
+    <row r="876">
       <c r="A876" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="877" spans="1:1">
+    <row r="877">
       <c r="A877" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="878" spans="1:1">
+    <row r="878">
       <c r="A878" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="879" spans="1:1">
+    <row r="879">
       <c r="A879" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="880" spans="1:1">
+    <row r="880">
       <c r="A880" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="881" spans="1:1">
+    <row r="881">
       <c r="A881" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="882" spans="1:1">
+    <row r="882">
       <c r="A882" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="883" spans="1:1">
+    <row r="883">
       <c r="A883" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="884" spans="1:1">
+    <row r="884">
       <c r="A884" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="885" spans="1:1">
+    <row r="885">
       <c r="A885" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="886" spans="1:1">
+    <row r="886">
       <c r="A886" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="887" spans="1:1">
+    <row r="887">
       <c r="A887" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="888" spans="1:1">
+    <row r="888">
       <c r="A888" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="889" spans="1:1">
+    <row r="889">
       <c r="A889" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="890" spans="1:1">
+    <row r="890">
       <c r="A890" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="891" spans="1:1">
+    <row r="891">
       <c r="A891" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="892" spans="1:1">
+    <row r="892">
       <c r="A892" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="893" spans="1:1">
+    <row r="893">
       <c r="A893" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="894" spans="1:1">
+    <row r="894">
       <c r="A894" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="895" spans="1:1">
+    <row r="895">
       <c r="A895" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="896" spans="1:1">
+    <row r="896">
       <c r="A896" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="897" spans="1:1">
+    <row r="897">
       <c r="A897" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="898" spans="1:1">
+    <row r="898">
       <c r="A898" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="899" spans="1:1">
+    <row r="899">
       <c r="A899" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="900" spans="1:1">
+    <row r="900">
       <c r="A900" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="901" spans="1:1">
+    <row r="901">
       <c r="A901" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="902" spans="1:1">
+    <row r="902">
       <c r="A902" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="903" spans="1:1">
+    <row r="903">
       <c r="A903" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="904" spans="1:1">
+    <row r="904">
       <c r="A904" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="905" spans="1:1">
+    <row r="905">
       <c r="A905" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="906" spans="1:1">
+    <row r="906">
       <c r="A906" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="907" spans="1:1">
+    <row r="907">
       <c r="A907" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="908" spans="1:1">
+    <row r="908">
       <c r="A908" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="909" spans="1:1">
+    <row r="909">
       <c r="A909" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="910" spans="1:1">
+    <row r="910">
       <c r="A910" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="911" spans="1:1">
+    <row r="911">
       <c r="A911" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="912" spans="1:1">
+    <row r="912">
       <c r="A912" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="913" spans="1:1">
+    <row r="913">
       <c r="A913" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="914" spans="1:1">
+    <row r="914">
       <c r="A914" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="915" spans="1:1">
+    <row r="915">
       <c r="A915" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="916" spans="1:1">
+    <row r="916">
       <c r="A916" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="917" spans="1:1">
+    <row r="917">
       <c r="A917" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="918" spans="1:1">
+    <row r="918">
       <c r="A918" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="919" spans="1:1">
+    <row r="919">
       <c r="A919" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="920" spans="1:1">
+    <row r="920">
       <c r="A920" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="921" spans="1:1">
+    <row r="921">
       <c r="A921" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="922" spans="1:1">
+    <row r="922">
       <c r="A922" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="923" spans="1:1">
+    <row r="923">
       <c r="A923" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="924" spans="1:1">
+    <row r="924">
       <c r="A924" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="925" spans="1:1">
+    <row r="925">
       <c r="A925" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="926" spans="1:1">
+    <row r="926">
       <c r="A926" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="927" spans="1:1">
+    <row r="927">
       <c r="A927" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="928" spans="1:1">
+    <row r="928">
       <c r="A928" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="929" spans="1:1">
+    <row r="929">
       <c r="A929" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="930" spans="1:1">
+    <row r="930">
       <c r="A930" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="931" spans="1:1">
+    <row r="931">
       <c r="A931" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="932" spans="1:1">
+    <row r="932">
       <c r="A932" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="933" spans="1:1">
+    <row r="933">
       <c r="A933" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="934" spans="1:1">
+    <row r="934">
       <c r="A934" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="935" spans="1:1">
+    <row r="935">
       <c r="A935" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="936" spans="1:1">
+    <row r="936">
       <c r="A936" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="937" spans="1:1">
+    <row r="937">
       <c r="A937" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="938" spans="1:1">
+    <row r="938">
       <c r="A938" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="939" spans="1:1">
+    <row r="939">
       <c r="A939" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="940" spans="1:1">
+    <row r="940">
       <c r="A940" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="941" spans="1:1">
+    <row r="941">
       <c r="A941" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="942" spans="1:1">
+    <row r="942">
       <c r="A942" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="943" spans="1:1">
+    <row r="943">
       <c r="A943" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="944" spans="1:1">
+    <row r="944">
       <c r="A944" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="945" spans="1:1">
+    <row r="945">
       <c r="A945" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="946" spans="1:1">
+    <row r="946">
       <c r="A946" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="947" spans="1:1">
+    <row r="947">
       <c r="A947" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="948" spans="1:1">
+    <row r="948">
       <c r="A948" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="949" spans="1:1">
+    <row r="949">
       <c r="A949" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="950" spans="1:1">
+    <row r="950">
       <c r="A950" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="951" spans="1:1">
+    <row r="951">
       <c r="A951" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="952" spans="1:1">
+    <row r="952">
       <c r="A952" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="953" spans="1:1">
+    <row r="953">
       <c r="A953" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="954" spans="1:1">
+    <row r="954">
       <c r="A954" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="955" spans="1:1">
+    <row r="955">
       <c r="A955" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="956" spans="1:1">
+    <row r="956">
       <c r="A956" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="957" spans="1:1">
+    <row r="957">
       <c r="A957" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="958" spans="1:1">
+    <row r="958">
       <c r="A958" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="959" spans="1:1">
+    <row r="959">
       <c r="A959" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="960" spans="1:1">
+    <row r="960">
       <c r="A960" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="961" spans="1:1">
+    <row r="961">
       <c r="A961" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="962" spans="1:1">
+    <row r="962">
       <c r="A962" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="963" spans="1:1">
+    <row r="963">
       <c r="A963" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="964" spans="1:1">
+    <row r="964">
       <c r="A964" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="965" spans="1:1">
+    <row r="965">
       <c r="A965" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="966" spans="1:1">
+    <row r="966">
       <c r="A966" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="967" spans="1:1">
+    <row r="967">
       <c r="A967" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="968" spans="1:1">
+    <row r="968">
       <c r="A968" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="969" spans="1:1">
+    <row r="969">
       <c r="A969" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="970" spans="1:1">
+    <row r="970">
       <c r="A970" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="971" spans="1:1">
+    <row r="971">
       <c r="A971" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="972" spans="1:1">
+    <row r="972">
       <c r="A972" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="973" spans="1:1">
+    <row r="973">
       <c r="A973" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="974" spans="1:1">
+    <row r="974">
       <c r="A974" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="975" spans="1:1">
+    <row r="975">
       <c r="A975" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="976" spans="1:1">
+    <row r="976">
       <c r="A976" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="977" spans="1:1">
+    <row r="977">
       <c r="A977" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="978" spans="1:1">
+    <row r="978">
       <c r="A978" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="979" spans="1:1">
+    <row r="979">
       <c r="A979" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="980" spans="1:1">
+    <row r="980">
       <c r="A980" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="981" spans="1:1">
+    <row r="981">
       <c r="A981" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="982" spans="1:1">
+    <row r="982">
       <c r="A982" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="983" spans="1:1">
+    <row r="983">
       <c r="A983" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="984" spans="1:1">
+    <row r="984">
       <c r="A984" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A27:G984 A1:G25 A26 E26:G26" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G984"/>
   </ignoredErrors>
 </worksheet>
 </file>